--- a/Sentences/prepared_sentences.xlsx
+++ b/Sentences/prepared_sentences.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -31,148 +31,451 @@
     <t xml:space="preserve">Kolejność znaków </t>
   </si>
   <si>
+    <t xml:space="preserve">Ilość</t>
+  </si>
+  <si>
     <t xml:space="preserve">Babcia i dziadek mają stary samochód.</t>
   </si>
   <si>
+    <t xml:space="preserve">BABCIA DZIADEK (PARA), SAMOCHÓD STARY, MA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj jestem zmęczony i chcę już iść spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA ZMĘCZONY, DZISIAJ JA CHCE, SPAĆ,  JUŻ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego wczoraj nie byłeś w szkole?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY,WCZORAJ,SZKOŁA , NIE BYŁO , DLACZEGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój brat ma duży dom i nowy samochód.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ BRAT,DOM DUŻY,SAMOCHÓD NOWY,MA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie jest mój stary telefon i samochód?</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ STARY,TELEFON , SAMOCHÓD ,GDZIE? </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój brat ma nowego kota, który bardzo lubi dużo spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ BRAT , KOT NOWY , MA , KOT,LUBI,BARDZO , DUŻO SPAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">My jesteśmy w domu i czekamy na tatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY,DOM , JESTEŚMY , TATA , CZEKAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego twój przyjaciel był wczoraj smutny?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ PRZYJACIEL , WCZORAJ , SMUTNY , DLACZEGO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy ty wiesz, gdzie jest moja mama i siostra?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY WIESZ , GDZIE , MAMA , SIOSTRA , JEST </t>
+  </si>
+  <si>
     <t xml:space="preserve">Chce mi się pić.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA,CHCE , PIĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Moja siostra uczy się migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">MOJA SIOSTRA , MIGAĆ , UCZY </t>
+  </si>
+  <si>
     <t xml:space="preserve">Co robisz w pracy?</t>
   </si>
   <si>
+    <t xml:space="preserve">PRACA , TY , ROBIĆ CO? </t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj byłem w szkole i uczyłem się migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA,WCZORAJ , SZKOŁA , BYŁO , MIGAĆ , UCZY </t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie rozumiem, co ty mówisz.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA,NIE ROZUMIEM , TY , MÓWIĆ CO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Wesoła kobieta idzie do domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA , WESOŁA , DOM , IŚĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Zmęczony brat idzie spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT,ZMĘCZONY , SPAĆ , IŚĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty lubisz uczyć się migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY LUBISZ,MIGAĆ,UCZYĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję za wodę i jedzenie.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ , WODA, JEDZENIE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj jest poniedziałek, idę do szkoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIŚ , PONIEDZIAŁEK , JA , SZKOŁA , PÓJDĘ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Brat lubi duże psy.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT,LUBI , DUŻE , PSY </t>
+  </si>
+  <si>
     <t xml:space="preserve">Smutny mężczyzna pije zimną kawę.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA , SMUTNY , KAWA , ZIMNA , PIJE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Kolega nie rozumie, co ja mówię.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA , NIE , ROZUMIEĆ , JA MÓWIĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie jest mój przyjaciel?</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ PRZYJACIEL , GDZIE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto wczoraj widział mojego psa?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO,WCZORAJ , MÓJ PIES , WIDZIAŁ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile pieniędzy chcesz?</t>
   </si>
   <si>
+    <t xml:space="preserve">PIENIĄDZE , TY , CHCIEĆ , ILE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy my idziemy do pracy?</t>
   </si>
   <si>
+    <t xml:space="preserve">MY , PRACA , PÓJŚĆ , KIEDY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty rozumiesz, co ona dzisiaj do ciebie mówi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego wy uczycie się migać z tym mężczyzną?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Siostra wczoraj była bardzo smutna.</t>
   </si>
   <si>
+    <t xml:space="preserve">SIOSTRA , WCZORAJ , BARDZO SMUTNA , BYŁA </t>
+  </si>
+  <si>
     <t xml:space="preserve">On nie słyszy, ale bardzo dobrze widzi.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON,NIE SŁYSZY , ALE WIDZI </t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie, ja nie chcę tego starego telefonu.</t>
   </si>
   <si>
+    <t xml:space="preserve">NIE, JA NIE CHCIEĆ ,TO,STARY TELEFON </t>
+  </si>
+  <si>
     <t xml:space="preserve">Siostra i brat czekają na nowy telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">SIOSTRA , BRAT , NOWY TELEFON , CZEKAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ty wczoraj nie chciałeś nam pomóc?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY,WCZORAJ , NIE CHCIEĆ , NAM POMÓC , DLACZEGO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak duży jest twój nowy dom?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY,DOM NOWY , DUŻY , JAK </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziadek nie słyszy, co mówi ta kobieta.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK , NIE SŁYCHAĆ , KOBIETA TA , MÓWIĆ CO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Smutna siostra czeka w domu na brata.</t>
   </si>
   <si>
+    <t xml:space="preserve">SIOSTRA , SMUTNA , DOM,BRAT, CZEKAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja wiem, że wy jesteście bardzo zmęczeni.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA , WIEM , WY,ZMĘCZENI, JEST </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ona kocha duże psy i bardzo małe koty.</t>
   </si>
   <si>
+    <t xml:space="preserve">ONA , KOCHAĆ , DUŻE PSY , MAŁE KOTY , BARDZO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzień dobry, ja idę dzisiaj rano pracować.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIEŃ DOBRY , JA , DZIŚ RANO , PRACA , PÓJŚĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Wesoły kolega wczoraj pomógł mi z samochodem.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA , WESOŁY , WCZORAJ , JA SAMOCHÓD , POMÓC </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mężczyzna nie słyszy, ale myśli i miga.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA , NIE SŁYCHAĆ , ALE , MYŚLEĆ , MIGAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak dobrze uczyć się migać w nowej szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">MIGAĆ, UCZY , NOWA SZKOŁA , DOBRZE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego wy nie chcecie migać w szkole?</t>
   </si>
   <si>
+    <t xml:space="preserve">WY,NIE CHCIEĆ , SZKOŁA , MIGAĆ , DLACZEGO </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziadek i babcia mają duży stary dom.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK , BABCIA , PARA , DUŻY STARY , DOM , MIEĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Brat ma kota i chce mieć małego psa.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT КОТ МА , MAŁY PIES , CHCE </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mały pies czeka na jedzenie i wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">MAŁY PIES, JEDZENIE , WODA , CZEKAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">To ważne, że my jesteśmy dzisiaj zdrowi.</t>
   </si>
   <si>
+    <t xml:space="preserve">WAŻNE , MY,DZIŚ , ZDROWY , BYĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Kolega z pracy uczy się migać ze mną.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA , PRACA , RAZEM , MIGAĆ , UCZYĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jestem chory i bardzo chcę dzisiaj spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA CHORY , DZIŚ , CHCĘ , SPAĆ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ty jesteś dzisiaj bardzo smutny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TY,DZIŚ , SMUTNY , DLACZEGO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chory brat nie chce dzisiaj iść do szkoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty myślisz, że ja jestem stary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano idę pracować do nowej szkoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty lubisz spać rano w nowym domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On pije zimną kawę rano przed pracą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mama myśli, że to jedzenie jest bardzo dobre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wesoły mężczyzna ma dużo pieniędzy na nowy dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My kochamy, kiedy oni są zdrowi i weseli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty jesteś zmęczony, więc nie chcesz teraz migać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano czekam na ważny telefon w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty wiesz, jak bardzo lubię uczyć się migać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj w nocy kolega pomógł mi w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My dzisiaj dużo pracujemy i nie chcemy spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak ty dzisiaj chcesz pracować, kiedy jesteś chory?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy oni uczą się migać z moim bratem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj rano ty byłeś bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja chcę dzisiaj spać w moim nowym domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj jest nowy dzień, więc jestem wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stary dziadek nie słyszy, co my mówimy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty i twój przyjaciel macie dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten stary kot nie chce dzisiaj jeść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego wy nie rozumiecie, co ja mówię?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto z was wie, jak dobrze migać?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile pieniędzy chcesz za ten mały samochód?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Który telefon jest stary, a który bardzo nowy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja wiem, że ty masz dzisiaj bardzo dobry dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On chce mieć duży dom i dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, ja wczoraj nie byłem w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój przyjaciel dzisiaj bardzo pomógł mi w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ty dzisiaj rano nie byłeś u babci?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolega czeka na mnie w starym samochodzie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata mówi, że ten nowy dom jest bardzo duży.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mężczyzna i kobieta jedzą dzisiaj w szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My widzimy, że oni są bardzo zmęczeni i chorzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto z was kocha tego małego, smutnego kota?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My lubimy mieć dużo pieniędzy w nowym roku.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rano zawsze piję kawę, a w nocy piję wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie my dzisiaj idziemy jeść i pić?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto wie, dlaczego ona jest dzisiaj bardzo chora?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja nie wiem, dlaczego on nie chce dzisiaj pomóc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, ale ja nie mam dzisiaj dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję, że ty rozumiesz, dlaczego jestem smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Który telefon jest twój, ten stary czy ten nowy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak on chce migać, kiedy nie widzi i nie słyszy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem byłem bardzo zdrowy i wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj myślę, co my chcemy jeść jutro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty myślisz, że ta kobieta ma dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja jestem chory i nie chcę dzisiaj jeść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On lubi gorącą herbatę w bardzo zimny dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zmęczony pies nie chce dzisiaj pić i jeść.</t>
   </si>
 </sst>
 </file>
@@ -187,21 +490,25 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -246,13 +553,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -378,423 +697,1270 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="84.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="0" t="s">
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="0" t="s">
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="0" t="s">
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="0" t="s">
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="0" t="s">
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="0" t="s">
+      <c r="B28" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
       <c r="B29" s="0" t="s">
-        <v>21</v>
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>29</v>
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>30</v>
+      <c r="B31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>31</v>
+      <c r="B32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>32</v>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>33</v>
+      <c r="B34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>34</v>
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>35</v>
+      <c r="B36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>36</v>
+      <c r="B37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>37</v>
+      <c r="B38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>38</v>
+      <c r="B39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>39</v>
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="0" t="s">
-        <v>40</v>
+      <c r="B41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>41</v>
+      <c r="B42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>42</v>
+      <c r="B43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>43</v>
+      <c r="B44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>44</v>
+      <c r="B45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>45</v>
+      <c r="B46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>46</v>
+      <c r="B47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>47</v>
+      <c r="B48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>48</v>
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>49</v>
+      <c r="B50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>50</v>
+      <c r="B51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -802,8 +1968,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Sentences/prepared_sentences.xlsx
+++ b/Sentences/prepared_sentences.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -476,6 +476,456 @@
   </si>
   <si>
     <t xml:space="preserve">Zmęczony pies nie chce dzisiaj pić i jeść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie, on dzisiaj nie ma pieniędzy na nowy telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że ja nie chciałem wczoraj pomóc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego my nie mamy dzisiaj gorącej kawy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co ty chcesz robić jutro wieczorem w domu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My jesteśmy dzisiaj weseli, bo mamy dużo czasu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję za wczoraj, to był bardzo dobry dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze mam dobry pomysł na nową książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam teraz czasu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jestem zmęczony więc idę spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam jutro urodzin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie jest mój klucz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brat ma nowy samochód.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twoja siostra jest bardzo wesoła.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia i dziadek są w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moja siostra ma małego psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj był dobry dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj jest poniedziałek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Który dzisiaj jest rok?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co robisz rano?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie jest twój telefon?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto ma mój klucz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Która kobieta to Twoja siostra?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja muszę iść do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy możesz mi pomóc?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolega chce kupić nową książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myślę, że to dobry pomysł.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wiesz, gdzie jest moja książka?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muszę dużo pracować, żeby mieć pieniądze.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To jest bardzo ważny dzień w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jestem bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy jesteś dzisiaj zdrowy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesteś bardzo dobrym kolegą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moja babcia jest już stara, ale zdrowa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę kupić ten samochód.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wy chcecie pić kawę czy herbatę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja nie mogę teraz iść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój kolega kupił dzisiaj telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widzę, że masz nowy samochód.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten mały pies zawsze czeka na mnie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy ten mężczyzna to twój tata?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro będę bardzo wesoły!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ten stary mężczyzna zawsze pije zimną herbatę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy Twój kolega chce kupić ten nowy samochód?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy ty słyszysz, co mówi do ciebie mama?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Który pomysł mojego brata lubisz najbardziej?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego wczoraj w nocy byłeś taki smutny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie mogę kupić dobrą i gorącą kawę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W poniedziałek rano często jestem bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj dziadek kupił mi bardzo dobrą książkę na urodziny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Często myślę o tym, co będę robić jutro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj jest bardzo ważny dzień dla mojego brata.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj moja siostra nie chciała iść ze mną do szkoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Często nie pamiętam, co mówiłem wczoraj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj nie mogę ci pomóc, bo muszę uczyć się do szkoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję za to, że wczoraj pomogłeś mi w szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze muszę czekać na mojego kolegę po pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jestem smutny, że ty nie możesz dzisiaj iść z nami.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo lubię, kiedy mój brat jest taki wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój brat zawsze chce mieć dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiem, że to jest bardzo ważny czas dla nas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ten mężczyzna teraz chce pracować w nocy we wtorek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile czasu musieliście wczoraj czekać na tatę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Która kobieta we wtorek rano już kupił ten samochód?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie w środę była mama, kiedy wy byliście już w domu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Który to był rok, kiedy dziadek kupił ten stary dom?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy pamiętasz, co w nocy mówił twój przyjaciel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile pieniędzy chcesz za ten stary telefon?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata miał wczoraj dużo pieniędzy, więc kupił mi książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On zawsze rano dużo pracuje, ale dzisiaj jest bardzo chory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja dzisiaj nie mam pieniędzy, więc nie mogę kupić tej herbaty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój przyjaciel ma nową pracę, więc dzisiaj jest wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta nowa szkoła zawsze uczy, dlaczego czas to pieniądz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój dobry przyjaciel zawsze wie, kiedy ja jestem smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata mojego kolegi to bardzo dobry i wesoły mężczyzna.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego dziadek nie chce dzisiaj pić ze mną gorącej kawy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego woda z domu zawsze rano jest taka zimna?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten duży i stary samochód mojego dziadka jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro będzie nowy dzień, więc my teraz idziemy już spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy mam w domu dużo czasu, bardzo lubię dużo myśleć.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze dziękuję za to, że mam dzisiaj gdzie spać</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo dziękuję za to, że twój brat rano uczy mnie migać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My musimy wiedzieć, dlaczego on wczoraj nie chciał iść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten stary mężczyzna bardzo często pije rano dużo gorącej kawy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ty zawsze dobrze wiesz, gdzie był mój klucz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobiety są bardzo zdrowe, bo często dużo pracują w dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myślałem, że ty wiesz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostań w poniedziałek u mnie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupiłem dla ciebie małą książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mama często chce pić kawę w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy zawsze jesteś taki smutny przed pracą?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego on nie może pomóc mamie z psem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uczymy się dzisiaj, a jutro idziemy spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twoja mama często robi mi herbatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten klucz jest dla mojego kolegi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie mama kupiła tę gorącą kawę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak dużo pieniędzy może mieć ta kobieta?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kocham pić herbatę z babcią i dziadkiem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że nie pamiętałem o twoich urodzinach.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy słyszałeś, co mówiła moja siostra?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musimy pracować w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musisz dużo jeść, żeby być zdrowym!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy widzieliście, jak on miga?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mam pomysł na nowy dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brat często ma dużo czasu dla mamy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta kobieta czeka na klucz przy szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze w poniedziałek piję zimną wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro nie mogę pracować, bo jestem bardzo chory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten rok jest dla nas bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój przyjaciel zawsze rozumie, co mówię.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj dużo myślałem o tej książce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego twój tata kupił taki stary samochód?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To był mój stary telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję ci za ten dobry dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto ma klucz do domu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mężczyzna czekał na ciebie przed szkołą wczoraj rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobiety często piją kawę rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój mały kot śpi pod starym samochodem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W nocy słyszałem psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego w poniedziałek pijesz zimną kawę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy masz czas na pracę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile książek wczoraj kupiłeś?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My lubimy dużo spać w dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twoja nowa praca jest bardzo ważna.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziadek i babcia zawsze mają dla mnie czas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja i mój brat chcemy zostać u kolegi na noc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie chcę pić wody z tobą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty zawsze wiesz, gdzie są moje pieniądze!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W poniedziałek rano kupiłem ten samochód dla mamy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy ty się uczysz, ja lubię spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze myślę, żeby kupić nowy telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On czeka w domu na ciebie i na tatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy twój pies lubi mojego małego kota?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta zimna noc była dla mnie bardzo smutna.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widzę cię dzisiaj przed moją pracą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czego ty wczoraj nie rozumiałeś?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy możemy iść do ciebie wieczorem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziadek zawsze pije gorącą herbatę w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto ci kupił tego psa i kota?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam cię za wczoraj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ty zawsze dużo mówisz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mam bardzo dobry pomysł na jutro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W szkole musimy uczyć się migać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój kolega wczoraj pił ze mną kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie są moje pieniądze z poniedziałku?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój tata bardzo kocha mojego brata.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobieta przed szkołą kupiła herbatę i kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty masz czas, żeby ze mną mówić?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro zostaniemy w starym domu dziadka.</t>
   </si>
 </sst>
 </file>
@@ -496,19 +946,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -553,7 +1000,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -566,11 +1013,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -697,8 +1140,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D301"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.32"/>
@@ -715,7 +1158,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -729,7 +1172,7 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -740,10 +1183,10 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -754,10 +1197,10 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -768,10 +1211,10 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -782,10 +1225,10 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -796,10 +1239,10 @@
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -810,10 +1253,10 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -824,10 +1267,10 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -838,10 +1281,10 @@
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -852,10 +1295,10 @@
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,10 +1309,10 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -880,10 +1323,10 @@
       <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,10 +1337,10 @@
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -908,10 +1351,10 @@
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -922,10 +1365,10 @@
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,10 +1379,10 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -950,10 +1393,10 @@
       <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -964,10 +1407,10 @@
       <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -978,10 +1421,10 @@
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -992,10 +1435,10 @@
       <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1006,10 +1449,10 @@
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,10 +1463,10 @@
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,10 +1477,10 @@
       <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,10 +1491,10 @@
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,10 +1505,10 @@
       <c r="B26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1076,10 +1519,10 @@
       <c r="B27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1087,10 +1530,10 @@
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,10 +1541,10 @@
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1112,10 +1555,10 @@
       <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1126,10 +1569,10 @@
       <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1140,10 +1583,10 @@
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1154,10 +1597,10 @@
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1168,10 +1611,10 @@
       <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1182,10 +1625,10 @@
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1196,10 +1639,10 @@
       <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1210,10 +1653,10 @@
       <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1224,10 +1667,10 @@
       <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,10 +1681,10 @@
       <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1252,10 +1695,10 @@
       <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1266,10 +1709,10 @@
       <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1280,10 +1723,10 @@
       <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,10 +1737,10 @@
       <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1308,10 +1751,10 @@
       <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1322,10 +1765,10 @@
       <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1336,10 +1779,10 @@
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1350,10 +1793,10 @@
       <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1364,10 +1807,10 @@
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1378,10 +1821,10 @@
       <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1392,10 +1835,10 @@
       <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1406,10 +1849,10 @@
       <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1417,10 +1860,10 @@
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1428,10 +1871,10 @@
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1439,10 +1882,10 @@
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1450,10 +1893,10 @@
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1461,10 +1904,10 @@
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1472,10 +1915,10 @@
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1483,10 +1926,10 @@
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1494,10 +1937,10 @@
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1505,10 +1948,10 @@
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,10 +1959,10 @@
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1527,10 +1970,10 @@
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1538,10 +1981,10 @@
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1549,10 +1992,10 @@
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1560,10 +2003,10 @@
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1571,10 +2014,10 @@
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1582,10 +2025,10 @@
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1593,10 +2036,10 @@
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1604,10 +2047,10 @@
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1615,10 +2058,10 @@
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1626,10 +2069,10 @@
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1637,10 +2080,10 @@
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1648,10 +2091,10 @@
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1659,10 +2102,10 @@
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1670,10 +2113,10 @@
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1681,10 +2124,10 @@
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,10 +2135,10 @@
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1703,10 +2146,10 @@
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1714,10 +2157,10 @@
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1725,10 +2168,10 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1736,10 +2179,10 @@
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1747,10 +2190,10 @@
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1758,10 +2201,10 @@
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1769,10 +2212,10 @@
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1780,10 +2223,10 @@
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1791,10 +2234,10 @@
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1802,10 +2245,10 @@
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1813,10 +2256,10 @@
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1824,10 +2267,10 @@
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1835,10 +2278,10 @@
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1846,10 +2289,10 @@
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1857,10 +2300,10 @@
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,10 +2311,10 @@
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,10 +2322,10 @@
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1890,10 +2333,10 @@
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1901,10 +2344,10 @@
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1912,10 +2355,10 @@
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1923,10 +2366,10 @@
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1934,10 +2377,10 @@
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1945,10 +2388,10 @@
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1956,20 +2399,1820 @@
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D101" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="D239" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="D240" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D252" s="2"/>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D253" s="2"/>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D254" s="2"/>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D255" s="2"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D256" s="2"/>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D257" s="2"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D258" s="2"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D259" s="2"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D260" s="2"/>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D261" s="2"/>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D262" s="2"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D263" s="2"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D264" s="2"/>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D265" s="2"/>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D266" s="2"/>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D267" s="2"/>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D268" s="2"/>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D269" s="2"/>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D270" s="2"/>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D271" s="2"/>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D272" s="2"/>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D273" s="2"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D274" s="2"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D275" s="2"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D276" s="2"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D277" s="2"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D278" s="2"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D279" s="2"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D280" s="2"/>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D281" s="2"/>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D282" s="2"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D283" s="2"/>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D284" s="2"/>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D285" s="2"/>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D286" s="2"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D287" s="2"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D288" s="2"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D289" s="2"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D290" s="2"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D291" s="2"/>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D292" s="2"/>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D293" s="2"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D294" s="2"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D295" s="2"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D296" s="2"/>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D297" s="2"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D298" s="2"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D299" s="2"/>
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D300" s="2"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D301" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Sentences/prepared_sentences.xlsx
+++ b/Sentences/prepared_sentences.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -331,601 +331,1201 @@
     <t xml:space="preserve">Chory brat nie chce dzisiaj iść do szkoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT, CHORY, DZISIAJ, SZKOŁA, IŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty myślisz, że ja jestem stary.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, MYŚLEĆ, JA, STARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro rano idę pracować do nowej szkoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, RANO, JA, PRACA, NOWA, SZKOŁA, IŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty lubisz spać rano w nowym domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, LUBIĆ, RANO, SPAĆ, NOWY, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">On pije zimną kawę rano przed pracą.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, RANO, PRZED, PRACA, KAWA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mama myśli, że to jedzenie jest bardzo dobre.</t>
   </si>
   <si>
+    <t xml:space="preserve">MAMA, MYŚLEĆ, JEDZENIE, TO, BARDZO, DOBRE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wesoły mężczyzna ma dużo pieniędzy na nowy dom.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, WESOŁY, PIENIĄDZE, DUŻO, NOWY, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">My kochamy, kiedy oni są zdrowi i weseli.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, KOCHAĆ, ONI, ZDROWY, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty jesteś zmęczony, więc nie chcesz teraz migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, ZMĘCZONY, WIĘC, TERAZ, MIGAĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro rano czekam na ważny telefon w pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, RANO, JA, PRACA, TELEFON, WAŻNY, CZEKAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty wiesz, jak bardzo lubię uczyć się migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WIEDZIEĆ, JA, BARDZO, LUBIĆ, UCZYĆ-SIĘ, MIGAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj w nocy kolega pomógł mi w pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, NOC, KOLEGA, MI, POMÓC, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">My dzisiaj dużo pracujemy i nie chcemy spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, DZISIAJ, PRACOWAĆ, DUŻO, SPAĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak ty dzisiaj chcesz pracować, kiedy jesteś chory?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DZISIAJ, JAK, PRACOWAĆ, CHORY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy oni uczą się migać z moim bratem?</t>
   </si>
   <si>
+    <t xml:space="preserve">ONI, KIEDY, UCZYĆ-SIĘ, MIGAĆ, MÓJ, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj rano ty byłeś bardzo zmęczony.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, RANO, TY, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja chcę dzisiaj spać w moim nowym domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, DZISIAJ, CHCIEĆ, SPAĆ, MÓJ, NOWY, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj jest nowy dzień, więc jestem wesoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, NOWY, DZIEŃ, WIĘC, JA, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stary dziadek nie słyszy, co my mówimy.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK, STARY, SŁYSZEĆ, NIE, MY, MÓWIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty i twój przyjaciel macie dużo pieniędzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY+TWÓJ, PRZYJACIEL, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten stary kot nie chce dzisiaj jeść.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOT, STARY, TEN, DZISIAJ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego wy nie rozumiecie, co ja mówię?</t>
   </si>
   <si>
+    <t xml:space="preserve">WY, DLACZEGO, ROZUMIEĆ, NIE, JA, MÓWIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto z was wie, jak dobrze migać?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, Z-WAS, WIEDZIEĆ, MIGAĆ, DOBRZE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile pieniędzy chcesz za ten mały samochód?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, CHCIEĆ, ILE, PIENIĄDZE, TEN, SAMOCHÓD, MAŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Który telefon jest stary, a który bardzo nowy?</t>
   </si>
   <si>
+    <t xml:space="preserve">TELEFON, KTÓRY, STARY, KTÓRY, NOWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja wiem, że ty masz dzisiaj bardzo dobry dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, WIEDZIEĆ, TY, DZISIAJ, DZIEŃ, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">On chce mieć duży dom i dużo pieniędzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, CHCIEĆ, DOM, DUŻY, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, ja wczoraj nie byłem w domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, JA, DOM, NIE-BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój przyjaciel dzisiaj bardzo pomógł mi w pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL, DZISIAJ, MI, BARDZO, POMÓC, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ty dzisiaj rano nie byłeś u babci?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DLACZEGO, DZISIAJ, RANO, BABCI, U, NIE-BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kolega czeka na mnie w starym samochodzie.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA, CZEKAĆ, NA-MNIE, SAMOCHÓD, STARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata mówi, że ten nowy dom jest bardzo duży.</t>
   </si>
   <si>
+    <t xml:space="preserve">TATA, MÓWIĆ, DOM, NOWY, TEN, BARDZO, DUŻY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mężczyzna i kobieta jedzą dzisiaj w szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, KOBIETA, DZISIAJ, SZKOŁA, JEŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">My widzimy, że oni są bardzo zmęczeni i chorzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, WIDZIEĆ, ONI, BARDZO, ZMĘCZONY, CHORY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto z was kocha tego małego, smutnego kota?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, Z-WAS, KOCHAĆ, KOT, MAŁY, SMUTNY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">My lubimy mieć dużo pieniędzy w nowym roku.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, LUBIĆ, PIENIĄDZE, DUŻO, NOWY, ROK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rano zawsze piję kawę, a w nocy piję wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">RANO, ZAWSZE, JA, KAWA, PIĆ, NOC, WODA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie my dzisiaj idziemy jeść i pić?</t>
   </si>
   <si>
+    <t xml:space="preserve">GDZIE, MY, DZISIAJ, IŚĆ, JEŚĆ, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto wie, dlaczego ona jest dzisiaj bardzo chora?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, WIEDZIEĆ, DLACZEGO, ONA, DZISIAJ, BARDZO, CHORA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja nie wiem, dlaczego on nie chce dzisiaj pomóc.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, WIEDZIEĆ, NIE, DLACZEGO, ON, DZISIAJ, POMÓC, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, ale ja nie mam dzisiaj dużo pieniędzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, JA, DZISIAJ, PIENIĄDZE, DUŻO, NIE-MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję, że ty rozumiesz, dlaczego jestem smutny.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ, TY, ROZUMIEĆ, DLACZEGO, JA, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Który telefon jest twój, ten stary czy ten nowy?</t>
   </si>
   <si>
+    <t xml:space="preserve">TELEFON, KTÓRY, TWÓJ, TEN, STARY, TEN, NOWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak on chce migać, kiedy nie widzi i nie słyszy?</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, JAK, MIGAĆ, CHCIEĆ, NIE-WIDZIEĆ, NIE-SŁYSZEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj wieczorem byłem bardzo zdrowy i wesoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, BARDZO, ZDROWY, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj myślę, co my chcemy jeść jutro.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, JA, MYŚLEĆ, MY, JUTRO, JEŚĆ, CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty myślisz, że ta kobieta ma dużo pieniędzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, MYŚLEĆ, KOBIETA, TA, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja jestem chory i nie chcę dzisiaj jeść.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CHORY, DZISIAJ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">On lubi gorącą herbatę w bardzo zimny dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, LUBIĆ, HERBATA, GORĄCA, DZIEŃ, BARDZO, ZIMNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zmęczony pies nie chce dzisiaj pić i jeść.</t>
   </si>
   <si>
+    <t xml:space="preserve">PIES, ZMĘCZONY, DZISIAJ, PIĆ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie, on dzisiaj nie ma pieniędzy na nowy telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, ON, PIENIĄDZE, TELEFON, NOWY, NIE-MA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, że ja nie chciałem wczoraj pomóc.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, JA, POMÓC, NIE-CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego my nie mamy dzisiaj gorącej kawy?</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, DZISIAJ, KAWA, GORĄCA, NIE-MIEĆ, DLACZEGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Co ty chcesz robić jutro wieczorem w domu?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, JUTRO, WIECZÓR, DOM, CO, ROBIĆ, CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">My jesteśmy dzisiaj weseli, bo mamy dużo czasu.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, DZISIAJ, WESOŁY, CZAS, DUŻO, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję za wczoraj, to był bardzo dobry dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ, WCZORAJ, DZIEŃ, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze mam dobry pomysł na nową książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, JA, POMYSŁ, DOBRY, NOWA, KSIĄŻKA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie mam teraz czasu</t>
   </si>
   <si>
+    <t xml:space="preserve">TERAZ, JA, CZAS, NIE-MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jestem zmęczony więc idę spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, ZMĘCZONY, WIĘC, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie mam jutro urodzin.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, JA, URODZINY, NIE-MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie jest mój klucz?</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, KLUCZ, GDZIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brat ma nowy samochód.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT, SAMOCHÓD, NOWY, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twoja siostra jest bardzo wesoła.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWOJA, SIOSTRA, BARDZO, WESOŁA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Babcia i dziadek są w domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">BABCIA+DZIADEK, DOM, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Moja siostra ma małego psa.</t>
   </si>
   <si>
+    <t xml:space="preserve">MOJA, SIOSTRA, PIES, MAŁY, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj był dobry dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, DZIEŃ, DOBRY, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj jest poniedziałek.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, PONIEDZIAŁEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Który dzisiaj jest rok?</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, ROK, KTÓRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Co robisz rano?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, RANO, CO, ROBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie jest twój telefon?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, TELEFON, GDZIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto ma mój klucz?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, MÓJ, KLUCZ, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Która kobieta to Twoja siostra?</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, KTÓRA, TWOJA, SIOSTRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja muszę iść do pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, MUSIEĆ, PRACA, IŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy możesz mi pomóc?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, MI, POMÓC, MOŻESZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kolega chce kupić nową książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA, CHCIEĆ, KUPIĆ, KSIĄŻKA, NOWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Myślę, że to dobry pomysł.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, MYŚLEĆ, TO, POMYSŁ, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy wiesz, gdzie jest moja książka?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WIEDZIEĆ, MOJA, KSIĄŻKA, GDZIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Muszę dużo pracować, żeby mieć pieniądze.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, MUSIEĆ, PRACOWAĆ, DUŻO, PIENIĄDZE, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">To jest bardzo ważny dzień w pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">TO, DZIEŃ, BARDZO, WAŻNY, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jestem bardzo zmęczony.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy jesteś dzisiaj zdrowy?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DZISIAJ, ZDROWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jesteś bardzo dobrym kolegą.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, KOLEGA, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Moja babcia jest już stara, ale zdrowa.</t>
   </si>
   <si>
+    <t xml:space="preserve">MOJA, BABCIA, STARA, ALE, ZDROWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chcę kupić ten samochód.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CHCIEĆ, KUPIĆ, SAMOCHÓD, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wy chcecie pić kawę czy herbatę?</t>
   </si>
   <si>
+    <t xml:space="preserve">WY, CHCIEĆ, PIĆ, KAWA, CZY, HERBATA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja nie mogę teraz iść.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, TERAZ, IŚĆ, NIE-MÓC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój kolega kupił dzisiaj telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, KOLEGA, DZISIAJ, TELEFON, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Widzę, że masz nowy samochód.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, WIDZIEĆ, TY, SAMOCHÓD, NOWY, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten mały pies zawsze czeka na mnie.</t>
   </si>
   <si>
+    <t xml:space="preserve">PIES, MAŁY, TEN, ZAWSZE, NA-MNIE, CZEKAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy ten mężczyzna to twój tata?</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, TEN, TWÓJ, TATA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro będę bardzo wesoły!</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, JA, BARDZO, WESOŁY, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ten stary mężczyzna zawsze pije zimną herbatę?</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, STARY, TEN, ZAWSZE, HERBATA, ZIMNA, PIĆ, DLACZEGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy Twój kolega chce kupić ten nowy samochód?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, KOLEGA, KIEDY, SAMOCHÓD, NOWY, TEN, KUPIĆ, CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy ty słyszysz, co mówi do ciebie mama?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, SŁYSZEĆ, MAMA, DO-CIEBIE, MÓWIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Który pomysł mojego brata lubisz najbardziej?</t>
   </si>
   <si>
+    <t xml:space="preserve">POMYSŁ, BRAT, MÓJ, KTÓRY, TY, LUBIĆ, NAJBARDZIEJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego wczoraj w nocy byłeś taki smutny?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WCZORAJ, NOC, DLACZEGO, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie mogę kupić dobrą i gorącą kawę?</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, GDZIE, KAWA, DOBRA, GORĄCA, KUPIĆ, MOŻNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">W poniedziałek rano często jestem bardzo zmęczony.</t>
   </si>
   <si>
+    <t xml:space="preserve">PONIEDZIAŁEK, RANO, CZĘSTO, JA, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj dziadek kupił mi bardzo dobrą książkę na urodziny.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, DZIADEK, MI, KSIĄŻKA, BARDZO, DOBRA, URODZINY, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Często myślę o tym, co będę robić jutro.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZĘSTO, JA, MYŚLEĆ, JUTRO, CO, ROBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj jest bardzo ważny dzień dla mojego brata.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, DZIEŃ, BARDZO, WAŻNY, MÓJ, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj moja siostra nie chciała iść ze mną do szkoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, MOJA, SIOSTRA, ZE-MNĄ, SZKOŁA, IŚĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Często nie pamiętam, co mówiłem wczoraj.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZĘSTO, JA, PAMIĘTAĆ, NIE, WCZORAJ, JA, MÓWIĆ, CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj nie mogę ci pomóc, bo muszę uczyć się do szkoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, JA, CI, POMÓC, NIE-MÓC, SZKOŁA, UCZYĆ-SIĘ, MUSIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję za to, że wczoraj pomogłeś mi w szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ, WCZORAJ, TY, MI, SZKOŁA, POMÓC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze muszę czekać na mojego kolegę po pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, JA, KOLEGA, MÓJ, PRACA, PO, CZEKAĆ, MUSIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jestem smutny, że ty nie możesz dzisiaj iść z nami.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, SMUTNY, TY, DZISIAJ, Z-NAMI, IŚĆ, NIE-MÓC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bardzo lubię, kiedy mój brat jest taki wesoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, BARDZO, LUBIĆ, MÓJ, BRAT, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój brat zawsze chce mieć dużo pieniędzy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, BRAT, ZAWSZE, PIENIĄDZE, DUŻO, CHCIEĆ, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wiem, że to jest bardzo ważny czas dla nas.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, WIEDZIEĆ, TO, CZAS, BARDZO, WAŻNY, DLA-NAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ten mężczyzna teraz chce pracować w nocy we wtorek?</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, TEN, TERAZ, DLACZEGO, NOC, WTOREK, PRACA, CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile czasu musieliście wczoraj czekać na tatę?</t>
   </si>
   <si>
+    <t xml:space="preserve">WY, WCZORAJ, TATA, NA, ILE, CZAS, CZEKAĆ, MUSIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Która kobieta we wtorek rano już kupił ten samochód?</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, KTÓRA, WTOREK, RANO, SAMOCHÓD, TEN, JUŻ, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie w środę była mama, kiedy wy byliście już w domu?</t>
   </si>
   <si>
+    <t xml:space="preserve">ŚRODA, MAMA, GDZIE, BYĆ, WY, DOM, JUŻ, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Który to był rok, kiedy dziadek kupił ten stary dom?</t>
   </si>
   <si>
+    <t xml:space="preserve">ROK, KTÓRY, TO, DZIADEK, DOM, STARY, TEN, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy pamiętasz, co w nocy mówił twój przyjaciel?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, PAMIĘTAĆ, TWÓJ, PRZYJACIEL, NOC, MÓWIĆ, CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile pieniędzy chcesz za ten stary telefon?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, CHCIEĆ, ILE, PIENIĄDZE, TELEFON, STARY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata miał wczoraj dużo pieniędzy, więc kupił mi książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, TATA, PIENIĄDZE, DUŻO, MIEĆ, WIĘC, MI, KSIĄŻKA, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">On zawsze rano dużo pracuje, ale dzisiaj jest bardzo chory.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, ZAWSZE, RANO, PRACOWAĆ, DUŻO, ALE, DZISIAJ, BARDZO, CHORY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja dzisiaj nie mam pieniędzy, więc nie mogę kupić tej herbaty.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, JA, PIENIĄDZE, NIE-MIEĆ, WIĘC, HERBATA, TA, KUPIĆ, NIE-MÓC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój przyjaciel ma nową pracę, więc dzisiaj jest wesoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL, PRACA, NOWA, MIEĆ, WIĘC, DZISIAJ, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ta nowa szkoła zawsze uczy, dlaczego czas to pieniądz.</t>
   </si>
   <si>
+    <t xml:space="preserve">SZKOŁA, NOWA, TA, ZAWSZE, UCZYĆ, DLACZEGO, CZAS, PIENIĄDZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój dobry przyjaciel zawsze wie, kiedy ja jestem smutny.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL, DOBRY, ZAWSZE, WIEDZIEĆ, JA, KIEDY, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata mojego kolegi to bardzo dobry i wesoły mężczyzna.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOLEGA, MÓJ, TATA, MĘŻCZYZNA, BARDZO, DOBRY, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego dziadek nie chce dzisiaj pić ze mną gorącej kawy?</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK, DLACZEGO, DZISIAJ, ZE-MNĄ, KAWA, GORĄCA, PIĆ, NIE-CHCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego woda z domu zawsze rano jest taka zimna?</t>
   </si>
   <si>
+    <t xml:space="preserve">WODA, DOM, ZAWSZE, RANO, DLACZEGO, ZIMNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten duży i stary samochód mojego dziadka jest bardzo dobry.</t>
   </si>
   <si>
+    <t xml:space="preserve">SAMOCHÓD, DUŻY, STARY, MÓJ, DZIADEK, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro będzie nowy dzień, więc my teraz idziemy już spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, DZIEŃ, NOWY, WIĘC, TERAZ, MY, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy mam w domu dużo czasu, bardzo lubię dużo myśleć.</t>
   </si>
   <si>
+    <t xml:space="preserve">DOM, JA, CZAS, DUŻO, MIEĆ, LUBIĆ, BARDZO, MYŚLEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze dziękuję za to, że mam dzisiaj gdzie spać</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, JA, DZIĘKOWAĆ, DZISIAJ, GDZIE, SPAĆ, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bardzo dziękuję za to, że twój brat rano uczy mnie migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">BARDZO, DZIĘKUJĘ, TWÓJ, BRAT, RANO, MNIE, MIGAĆ, UCZYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">My musimy wiedzieć, dlaczego on wczoraj nie chciał iść.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, MUSIEĆ, WIEDZIEĆ, DLACZEGO, ON, WCZORAJ, IŚĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten stary mężczyzna bardzo często pije rano dużo gorącej kawy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, STARY, TEN, CZĘSTO, RANO, KAWA, GORĄCA, DUŻO, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ty zawsze dobrze wiesz, gdzie był mój klucz?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DLACZEGO, ZAWSZE, DOBRZE, WIEDZIEĆ, MÓJ, KLUCZ, GDZIE, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kobiety są bardzo zdrowe, bo często dużo pracują w dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETY, BARDZO, ZDROWE, BO, CZĘSTO, DZIEŃ, PRACOWAĆ, DUŻO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Myślałem, że ty wiesz.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, MYŚLEĆ, TY, WIEDZIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zostań w poniedziałek u mnie.</t>
   </si>
   <si>
+    <t xml:space="preserve">PONIEDZIAŁEK, U-MNIE, ZOSTAŃ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kupiłem dla ciebie małą książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, DLA-CIEBIE, KSIĄŻKA, MAŁA, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mama często chce pić kawę w nocy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MAMA, CZĘSTO, NOC, KAWA, PIĆ, CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy zawsze jesteś taki smutny przed pracą?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, ZAWSZE, PRACA, PRZED, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego on nie może pomóc mamie z psem?</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, DLACZEGO, MAMA, PIES, POMÓC, NIE-MÓC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, KOBIETA, MĘŻCZYZNA, TEMU, DZIĘKOWAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Uczymy się dzisiaj, a jutro idziemy spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, MY, UCZYĆ-SIĘ, JUTRO, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twoja mama często robi mi herbatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWOJA, MAMA, CZĘSTO, MI, HERBATA, ROBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten klucz jest dla mojego kolegi.</t>
   </si>
   <si>
+    <t xml:space="preserve">KLUCZ, TEN, KOLEGA, MÓJ, DLA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie mama kupiła tę gorącą kawę?</t>
   </si>
   <si>
+    <t xml:space="preserve">MAMA, GDZIE, KAWA, GORĄCA, TA, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak dużo pieniędzy może mieć ta kobieta?</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, TA, PIENIĄDZE, ILE, MIEĆ, MOŻE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kocham pić herbatę z babcią i dziadkiem.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, KOCHAĆ, HERBATA, PIĆ, BABCIA, DZIADEK, Z</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, że nie pamiętałem o twoich urodzinach.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, JA, TWOJE, URODZINY, PAMIĘTAĆ, NIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy słyszałeś, co mówiła moja siostra?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, SŁYSZEĆ, MOJA, SIOSTRA, MÓWIĆ, CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Musimy pracować w nocy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, MUSIEĆ, NOC, PRACOWAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Musisz dużo jeść, żeby być zdrowym!</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, MUSIEĆ, JEŚĆ, DUŻO, ZDROWY, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy widzieliście, jak on miga?</t>
   </si>
   <si>
+    <t xml:space="preserve">WY, WIDZIEĆ, ON, MIGAĆ, JAK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mam pomysł na nowy dom.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, POMYSŁ, DOM, NOWY, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brat często ma dużo czasu dla mamy.</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAT, CZĘSTO, CZAS, DUŻO, MAMA, DLA, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ta kobieta czeka na klucz przy szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, TA, SZKOŁA, PRZY, KLUCZ, CZEKAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze w poniedziałek piję zimną wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, PONIEDZIAŁEK, JA, WODA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro nie mogę pracować, bo jestem bardzo chory.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, JA, PRACOWAĆ, NIE-MÓC, BO, JA, BARDZO, CHORY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten rok jest dla nas bardzo dobry.</t>
   </si>
   <si>
+    <t xml:space="preserve">ROK, TEN, DLA-NAS, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój przyjaciel zawsze rozumie, co mówię.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL, ZAWSZE, ROZUMIEĆ, JA, MÓWIĆ, CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj dużo myślałem o tej książce.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, JA, MYŚLEĆ, DUŻO, KSIĄŻKA, TA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego twój tata kupił taki stary samochód?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, TATA, DLACZEGO, SAMOCHÓD, STARY, TAKI, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, LUBIĆ, NIE, TY, SZKOŁA, PO, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
     <t xml:space="preserve">To był mój stary telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">TO, MÓJ, TELEFON, STARY, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję ci za ten dobry dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ, CI, DZIEŃ, DOBRY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto ma klucz do domu?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, KLUCZ, DOM, DO, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mężczyzna czekał na ciebie przed szkołą wczoraj rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, WCZORAJ, RANO, SZKOŁA, PRZED, NA-CIEBIE, CZEKAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kobiety często piją kawę rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETY, CZĘSTO, RANO, KAWA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój mały kot śpi pod starym samochodem.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, KOT, MAŁY, SAMOCHÓD, STARY, POD, SPAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">W nocy słyszałem psa.</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC, JA, PIES, SŁYSZEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego w poniedziałek pijesz zimną kawę?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, PONIEDZIAŁEK, DLACZEGO, KAWA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy masz czas na pracę?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, KIEDY, CZAS, PRACA, NA, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile książek wczoraj kupiłeś?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WCZORAJ, KSIĄŻKA, ILE, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">My lubimy dużo spać w dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, DZIEŃ, SPAĆ, DUŻO, LUBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twoja nowa praca jest bardzo ważna.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWOJA, PRACA, NOWA, BARDZO, WAŻNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziadek i babcia zawsze mają dla mnie czas.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK+BABCIA, ZAWSZE, MI, CZAS, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja i mój brat chcemy zostać u kolegi na noc.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA+MÓJ, BRAT, KOLEGA, U, NOC, ZOSTAĆ, CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie chcę pić wody z tobą.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, Z-TOBĄ, WODA, PIĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty zawsze wiesz, gdzie są moje pieniądze!</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, ZAWSZE, WIEDZIEĆ, MOJE, PIENIĄDZE, GDZIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">W poniedziałek rano kupiłem ten samochód dla mamy.</t>
   </si>
   <si>
+    <t xml:space="preserve">PONIEDZIAŁEK, RANO, JA, SAMOCHÓD, TEN, MAMA, DLA, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy ty się uczysz, ja lubię spać.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, UCZYĆ-SIĘ, KIEDY, JA, SPAĆ, LUBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze myślę, żeby kupić nowy telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, JA, MYŚLEĆ, TELEFON, NOWY, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">On czeka w domu na ciebie i na tatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">ON, DOM, NA-CIEBIE, I, TATA, CZEKAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy twój pies lubi mojego małego kota?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, PIES, MÓJ, KOT, MAŁY, LUBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ta zimna noc była dla mnie bardzo smutna.</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC, ZIMNA, TA, DLA-MNIE, BARDZO, SMUTNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Widzę cię dzisiaj przed moją pracą.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, DZISIAJ, CIĘ, WIDZIEĆ, PRACA, MOJA, PRZED</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czego ty wczoraj nie rozumiałeś?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WCZORAJ, CO, ROZUMIEĆ, NIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy możemy iść do ciebie wieczorem?</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, WIECZÓR, DO-CIEBIE, IŚĆ, MOŻNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziadek zawsze pije gorącą herbatę w nocy.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK, ZAWSZE, NOC, HERBATA, GORĄCA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto ci kupił tego psa i kota?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, CI, PIES, TEN, I, KOT, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam cię za wczoraj.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, CI, WCZORAJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ty zawsze dużo mówisz?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DLACZEGO, ZAWSZE, MÓWIĆ, DUŻO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mam bardzo dobry pomysł na jutro.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, POMYSŁ, BARDZO, DOBRY, JUTRO, NA, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">W szkole musimy uczyć się migać.</t>
   </si>
   <si>
+    <t xml:space="preserve">SZKOŁA, MY, MUSIEĆ, UCZYĆ-SIĘ, MIGAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twój kolega wczoraj pił ze mną kawę.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, KOLEGA, WCZORAJ, ZE-MNĄ, KAWA, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie są moje pieniądze z poniedziałku?</t>
   </si>
   <si>
+    <t xml:space="preserve">MOJE, PIENIĄDZE, PONIEDZIAŁEK, Z, GDZIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój tata bardzo kocha mojego brata.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, TATA, BARDZO, KOCHAĆ, MÓJ, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kobieta przed szkołą kupiła herbatę i kawę.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, SZKOŁA, PRZED, HERBATA, I, KAWA, KUPIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty masz czas, żeby ze mną mówić?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, CZAS, ZE-MNĄ, MÓWIĆ, NA, MIEĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro zostaniemy w starym domu dziadka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUTRO, MY, DOM, STARY, DZIADEK, ZOSTAĆ</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1600,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1014,6 +1614,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1144,7 +1748,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="84.29"/>
   </cols>
   <sheetData>
@@ -1863,6 +2467,9 @@
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="C52" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="D52" s="2" t="n">
         <v>0</v>
       </c>
@@ -1872,7 +2479,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0</v>
@@ -1883,7 +2493,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0</v>
@@ -1894,7 +2507,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0</v>
@@ -1905,7 +2521,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0</v>
@@ -1916,7 +2535,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0</v>
@@ -1927,7 +2549,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0</v>
@@ -1938,7 +2563,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0</v>
@@ -1949,7 +2577,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0</v>
@@ -1960,7 +2591,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0</v>
@@ -1971,7 +2605,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0</v>
@@ -1982,7 +2619,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0</v>
@@ -1993,7 +2633,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0</v>
@@ -2004,7 +2647,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>115</v>
+        <v>128</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0</v>
@@ -2015,7 +2661,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0</v>
@@ -2026,7 +2675,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0</v>
@@ -2037,7 +2689,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0</v>
@@ -2048,7 +2703,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
@@ -2059,7 +2717,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -2070,7 +2731,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0</v>
@@ -2081,7 +2745,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>122</v>
+        <v>142</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0</v>
@@ -2092,7 +2759,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0</v>
@@ -2103,7 +2773,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>124</v>
+        <v>146</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0</v>
@@ -2114,7 +2787,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>125</v>
+        <v>148</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0</v>
@@ -2125,7 +2801,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>126</v>
+        <v>150</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0</v>
@@ -2136,7 +2815,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>127</v>
+        <v>152</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0</v>
@@ -2147,7 +2829,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>128</v>
+        <v>154</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0</v>
@@ -2158,7 +2843,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>129</v>
+        <v>156</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0</v>
@@ -2169,7 +2857,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>130</v>
+        <v>158</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0</v>
@@ -2180,7 +2871,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>131</v>
+        <v>160</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0</v>
@@ -2191,7 +2885,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>132</v>
+        <v>162</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0</v>
@@ -2202,7 +2899,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2913,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>134</v>
+        <v>166</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0</v>
@@ -2224,7 +2927,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>135</v>
+        <v>168</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0</v>
@@ -2235,7 +2941,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>136</v>
+        <v>170</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0</v>
@@ -2246,7 +2955,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0</v>
@@ -2257,7 +2969,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>138</v>
+        <v>174</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0</v>
@@ -2268,7 +2983,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>139</v>
+        <v>176</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0</v>
@@ -2279,7 +2997,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>140</v>
+        <v>178</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0</v>
@@ -2290,7 +3011,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>141</v>
+        <v>180</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0</v>
@@ -2301,7 +3025,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>142</v>
+        <v>182</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0</v>
@@ -2312,7 +3039,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>143</v>
+        <v>184</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0</v>
@@ -2323,7 +3053,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>144</v>
+        <v>186</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0</v>
@@ -2334,7 +3067,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>145</v>
+        <v>188</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0</v>
@@ -2345,7 +3081,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>146</v>
+        <v>190</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0</v>
@@ -2356,7 +3095,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>147</v>
+        <v>192</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0</v>
@@ -2367,7 +3109,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>148</v>
+        <v>194</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0</v>
@@ -2378,7 +3123,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>149</v>
+        <v>196</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0</v>
@@ -2389,7 +3137,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>150</v>
+        <v>198</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0</v>
@@ -2400,7 +3151,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>151</v>
+        <v>200</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0</v>
@@ -2410,8 +3164,11 @@
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>152</v>
+      <c r="B102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0</v>
@@ -2421,8 +3178,11 @@
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>153</v>
+      <c r="B103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0</v>
@@ -2432,8 +3192,11 @@
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>154</v>
+      <c r="B104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0</v>
@@ -2443,8 +3206,11 @@
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="0" t="s">
-        <v>155</v>
+      <c r="B105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0</v>
@@ -2454,8 +3220,11 @@
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>156</v>
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0</v>
@@ -2465,8 +3234,11 @@
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="0" t="s">
-        <v>157</v>
+      <c r="B107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0</v>
@@ -2476,8 +3248,11 @@
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="0" t="s">
-        <v>158</v>
+      <c r="B108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0</v>
@@ -2487,8 +3262,11 @@
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="0" t="s">
-        <v>159</v>
+      <c r="B109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0</v>
@@ -2498,8 +3276,11 @@
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>160</v>
+      <c r="B110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0</v>
@@ -2509,8 +3290,11 @@
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="0" t="s">
-        <v>161</v>
+      <c r="B111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0</v>
@@ -2520,8 +3304,11 @@
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="0" t="s">
-        <v>162</v>
+      <c r="B112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0</v>
@@ -2531,8 +3318,11 @@
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="0" t="s">
-        <v>163</v>
+      <c r="B113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0</v>
@@ -2542,8 +3332,11 @@
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="0" t="s">
-        <v>164</v>
+      <c r="B114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>227</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0</v>
@@ -2553,8 +3346,11 @@
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="0" t="s">
-        <v>165</v>
+      <c r="B115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>229</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0</v>
@@ -2564,8 +3360,11 @@
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="0" t="s">
-        <v>166</v>
+      <c r="B116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>231</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0</v>
@@ -2575,8 +3374,11 @@
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="0" t="s">
-        <v>167</v>
+      <c r="B117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>233</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0</v>
@@ -2586,8 +3388,11 @@
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="0" t="s">
-        <v>168</v>
+      <c r="B118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0</v>
@@ -2597,8 +3402,11 @@
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="0" t="s">
-        <v>169</v>
+      <c r="B119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>237</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0</v>
@@ -2608,8 +3416,11 @@
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="0" t="s">
-        <v>170</v>
+      <c r="B120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0</v>
@@ -2619,8 +3430,11 @@
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="0" t="s">
-        <v>171</v>
+      <c r="B121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0</v>
@@ -2630,8 +3444,11 @@
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>172</v>
+      <c r="B122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0</v>
@@ -2641,8 +3458,11 @@
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="0" t="s">
-        <v>173</v>
+      <c r="B123" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0</v>
@@ -2652,8 +3472,11 @@
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="0" t="s">
-        <v>174</v>
+      <c r="B124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0</v>
@@ -2663,8 +3486,11 @@
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="0" t="s">
-        <v>175</v>
+      <c r="B125" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0</v>
@@ -2674,8 +3500,11 @@
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="0" t="s">
-        <v>176</v>
+      <c r="B126" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0</v>
@@ -2685,8 +3514,11 @@
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="0" t="s">
-        <v>177</v>
+      <c r="B127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0</v>
@@ -2696,8 +3528,11 @@
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="0" t="s">
-        <v>178</v>
+      <c r="B128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>255</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0</v>
@@ -2707,8 +3542,11 @@
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="0" t="s">
-        <v>179</v>
+      <c r="B129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0</v>
@@ -2718,8 +3556,11 @@
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="0" t="s">
-        <v>180</v>
+      <c r="B130" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>259</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0</v>
@@ -2729,8 +3570,11 @@
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="0" t="s">
-        <v>181</v>
+      <c r="B131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0</v>
@@ -2740,8 +3584,11 @@
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="0" t="s">
-        <v>182</v>
+      <c r="B132" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0</v>
@@ -2751,8 +3598,11 @@
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="0" t="s">
-        <v>183</v>
+      <c r="B133" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0</v>
@@ -2762,8 +3612,11 @@
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="0" t="s">
-        <v>184</v>
+      <c r="B134" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0</v>
@@ -2773,8 +3626,11 @@
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="0" t="s">
-        <v>185</v>
+      <c r="B135" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0</v>
@@ -2784,8 +3640,11 @@
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="0" t="s">
-        <v>186</v>
+      <c r="B136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0</v>
@@ -2795,8 +3654,11 @@
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="0" t="s">
-        <v>187</v>
+      <c r="B137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>273</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0</v>
@@ -2806,8 +3668,11 @@
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="0" t="s">
-        <v>188</v>
+      <c r="B138" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0</v>
@@ -2817,8 +3682,11 @@
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="0" t="s">
-        <v>189</v>
+      <c r="B139" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>277</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0</v>
@@ -2828,8 +3696,11 @@
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="0" t="s">
-        <v>190</v>
+      <c r="B140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0</v>
@@ -2839,8 +3710,11 @@
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="0" t="s">
-        <v>191</v>
+      <c r="B141" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0</v>
@@ -2850,8 +3724,11 @@
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="0" t="s">
-        <v>192</v>
+      <c r="B142" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0</v>
@@ -2861,8 +3738,11 @@
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="0" t="s">
-        <v>193</v>
+      <c r="B143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0</v>
@@ -2872,8 +3752,11 @@
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="0" t="s">
-        <v>194</v>
+      <c r="B144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0</v>
@@ -2883,8 +3766,11 @@
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="0" t="s">
-        <v>195</v>
+      <c r="B145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0</v>
@@ -2894,8 +3780,11 @@
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="0" t="s">
-        <v>196</v>
+      <c r="B146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0</v>
@@ -2905,8 +3794,11 @@
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="0" t="s">
-        <v>197</v>
+      <c r="B147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>293</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0</v>
@@ -2916,8 +3808,11 @@
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="0" t="s">
-        <v>198</v>
+      <c r="B148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0</v>
@@ -2927,8 +3822,11 @@
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="0" t="s">
-        <v>199</v>
+      <c r="B149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>297</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0</v>
@@ -2938,8 +3836,11 @@
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="0" t="s">
-        <v>200</v>
+      <c r="B150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0</v>
@@ -2949,8 +3850,11 @@
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="0" t="s">
-        <v>201</v>
+      <c r="B151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0</v>
@@ -2960,8 +3864,11 @@
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="0" t="s">
-        <v>202</v>
+      <c r="B152" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0</v>
@@ -2971,8 +3878,11 @@
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="0" t="s">
-        <v>203</v>
+      <c r="B153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0</v>
@@ -2982,8 +3892,11 @@
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="0" t="s">
-        <v>204</v>
+      <c r="B154" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>307</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0</v>
@@ -2993,8 +3906,11 @@
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="0" t="s">
-        <v>205</v>
+      <c r="B155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0</v>
@@ -3004,8 +3920,11 @@
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="0" t="s">
-        <v>206</v>
+      <c r="B156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0</v>
@@ -3015,8 +3934,11 @@
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="0" t="s">
-        <v>207</v>
+      <c r="B157" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>313</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0</v>
@@ -3026,8 +3948,11 @@
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="0" t="s">
-        <v>208</v>
+      <c r="B158" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0</v>
@@ -3037,8 +3962,11 @@
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="0" t="s">
-        <v>209</v>
+      <c r="B159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>317</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0</v>
@@ -3048,8 +3976,11 @@
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="0" t="s">
-        <v>210</v>
+      <c r="B160" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0</v>
@@ -3059,8 +3990,11 @@
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="0" t="s">
-        <v>211</v>
+      <c r="B161" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0</v>
@@ -3070,8 +4004,11 @@
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="0" t="s">
-        <v>212</v>
+      <c r="B162" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0</v>
@@ -3081,8 +4018,11 @@
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="0" t="s">
-        <v>213</v>
+      <c r="B163" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0</v>
@@ -3092,8 +4032,11 @@
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="0" t="s">
-        <v>214</v>
+      <c r="B164" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>327</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0</v>
@@ -3103,8 +4046,11 @@
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="0" t="s">
-        <v>215</v>
+      <c r="B165" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>329</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0</v>
@@ -3114,8 +4060,11 @@
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="0" t="s">
-        <v>216</v>
+      <c r="B166" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>331</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0</v>
@@ -3125,8 +4074,11 @@
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="0" t="s">
-        <v>217</v>
+      <c r="B167" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>333</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0</v>
@@ -3136,8 +4088,11 @@
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="0" t="s">
-        <v>218</v>
+      <c r="B168" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>335</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0</v>
@@ -3147,8 +4102,11 @@
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="0" t="s">
-        <v>219</v>
+      <c r="B169" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0</v>
@@ -3158,8 +4116,11 @@
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="0" t="s">
-        <v>220</v>
+      <c r="B170" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>339</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0</v>
@@ -3169,8 +4130,11 @@
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="0" t="s">
-        <v>221</v>
+      <c r="B171" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>341</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0</v>
@@ -3180,8 +4144,11 @@
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="0" t="s">
-        <v>222</v>
+      <c r="B172" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>343</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0</v>
@@ -3191,8 +4158,11 @@
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="0" t="s">
-        <v>223</v>
+      <c r="B173" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>345</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0</v>
@@ -3202,8 +4172,11 @@
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="0" t="s">
-        <v>224</v>
+      <c r="B174" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>347</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0</v>
@@ -3213,8 +4186,11 @@
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="0" t="s">
-        <v>225</v>
+      <c r="B175" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>349</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0</v>
@@ -3224,8 +4200,11 @@
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="0" t="s">
-        <v>226</v>
+      <c r="B176" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0</v>
@@ -3235,8 +4214,11 @@
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="0" t="s">
-        <v>227</v>
+      <c r="B177" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>353</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0</v>
@@ -3246,8 +4228,11 @@
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="0" t="s">
-        <v>228</v>
+      <c r="B178" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0</v>
@@ -3257,8 +4242,11 @@
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="0" t="s">
-        <v>229</v>
+      <c r="B179" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>357</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0</v>
@@ -3268,8 +4256,11 @@
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="0" t="s">
-        <v>230</v>
+      <c r="B180" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0</v>
@@ -3279,8 +4270,11 @@
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="0" t="s">
-        <v>231</v>
+      <c r="B181" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0</v>
@@ -3290,8 +4284,11 @@
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="0" t="s">
-        <v>232</v>
+      <c r="B182" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0</v>
@@ -3301,8 +4298,11 @@
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="0" t="s">
-        <v>233</v>
+      <c r="B183" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>365</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0</v>
@@ -3312,8 +4312,11 @@
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="0" t="s">
-        <v>234</v>
+      <c r="B184" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0</v>
@@ -3323,8 +4326,11 @@
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="0" t="s">
-        <v>235</v>
+      <c r="B185" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>369</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0</v>
@@ -3334,8 +4340,11 @@
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="0" t="s">
-        <v>236</v>
+      <c r="B186" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0</v>
@@ -3345,8 +4354,11 @@
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="0" t="s">
-        <v>237</v>
+      <c r="B187" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0</v>
@@ -3356,8 +4368,11 @@
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="0" t="s">
-        <v>238</v>
+      <c r="B188" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>375</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0</v>
@@ -3367,8 +4382,11 @@
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="0" t="s">
-        <v>239</v>
+      <c r="B189" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>377</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0</v>
@@ -3378,8 +4396,11 @@
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="0" t="s">
-        <v>240</v>
+      <c r="B190" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>379</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0</v>
@@ -3389,8 +4410,11 @@
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="0" t="s">
-        <v>241</v>
+      <c r="B191" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>381</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0</v>
@@ -3400,8 +4424,11 @@
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="0" t="s">
-        <v>242</v>
+      <c r="B192" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0</v>
@@ -3411,8 +4438,11 @@
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="0" t="s">
-        <v>243</v>
+      <c r="B193" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0</v>
@@ -3422,8 +4452,11 @@
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="0" t="s">
-        <v>244</v>
+      <c r="B194" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>387</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0</v>
@@ -3433,8 +4466,11 @@
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="0" t="s">
-        <v>245</v>
+      <c r="B195" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0</v>
@@ -3444,8 +4480,11 @@
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="0" t="s">
-        <v>246</v>
+      <c r="B196" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>391</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0</v>
@@ -3455,8 +4494,11 @@
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="0" t="s">
-        <v>247</v>
+      <c r="B197" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>393</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0</v>
@@ -3466,8 +4508,11 @@
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="0" t="s">
-        <v>248</v>
+      <c r="B198" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>395</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0</v>
@@ -3477,8 +4522,11 @@
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="0" t="s">
-        <v>249</v>
+      <c r="B199" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0</v>
@@ -3488,8 +4536,11 @@
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="0" t="s">
-        <v>250</v>
+      <c r="B200" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0</v>
@@ -3499,8 +4550,11 @@
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="0" t="s">
-        <v>251</v>
+      <c r="B201" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0</v>
@@ -3510,8 +4564,11 @@
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="0" t="s">
-        <v>252</v>
+      <c r="B202" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>403</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0</v>
@@ -3521,8 +4578,11 @@
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="0" t="s">
-        <v>253</v>
+      <c r="B203" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>405</v>
       </c>
       <c r="D203" s="2" t="n">
         <v>0</v>
@@ -3532,8 +4592,11 @@
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="0" t="s">
-        <v>254</v>
+      <c r="B204" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>407</v>
       </c>
       <c r="D204" s="2" t="n">
         <v>0</v>
@@ -3543,8 +4606,11 @@
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="0" t="s">
-        <v>255</v>
+      <c r="B205" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="D205" s="2" t="n">
         <v>0</v>
@@ -3554,8 +4620,11 @@
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="0" t="s">
-        <v>256</v>
+      <c r="B206" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>411</v>
       </c>
       <c r="D206" s="2" t="n">
         <v>0</v>
@@ -3565,8 +4634,11 @@
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="0" t="s">
-        <v>257</v>
+      <c r="B207" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>413</v>
       </c>
       <c r="D207" s="2" t="n">
         <v>0</v>
@@ -3576,8 +4648,11 @@
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="0" t="s">
-        <v>258</v>
+      <c r="B208" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>415</v>
       </c>
       <c r="D208" s="2" t="n">
         <v>0</v>
@@ -3587,8 +4662,11 @@
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="0" t="s">
-        <v>259</v>
+      <c r="B209" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>417</v>
       </c>
       <c r="D209" s="2" t="n">
         <v>0</v>
@@ -3598,8 +4676,11 @@
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="0" t="s">
-        <v>260</v>
+      <c r="B210" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>419</v>
       </c>
       <c r="D210" s="2" t="n">
         <v>0</v>
@@ -3609,8 +4690,11 @@
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="0" t="s">
-        <v>261</v>
+      <c r="B211" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>421</v>
       </c>
       <c r="D211" s="2" t="n">
         <v>0</v>
@@ -3620,8 +4704,11 @@
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="0" t="s">
-        <v>262</v>
+      <c r="B212" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="D212" s="2" t="n">
         <v>0</v>
@@ -3631,8 +4718,11 @@
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="0" t="s">
-        <v>263</v>
+      <c r="B213" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>425</v>
       </c>
       <c r="D213" s="2" t="n">
         <v>0</v>
@@ -3642,8 +4732,11 @@
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="0" t="s">
-        <v>264</v>
+      <c r="B214" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>427</v>
       </c>
       <c r="D214" s="2" t="n">
         <v>0</v>
@@ -3653,8 +4746,11 @@
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
-      <c r="B215" s="0" t="s">
-        <v>265</v>
+      <c r="B215" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>429</v>
       </c>
       <c r="D215" s="2" t="n">
         <v>0</v>
@@ -3664,8 +4760,11 @@
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="0" t="s">
-        <v>266</v>
+      <c r="B216" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>431</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>0</v>
@@ -3675,8 +4774,11 @@
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="0" t="s">
-        <v>267</v>
+      <c r="B217" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>0</v>
@@ -3686,8 +4788,11 @@
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
-      <c r="B218" s="0" t="s">
-        <v>268</v>
+      <c r="B218" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>435</v>
       </c>
       <c r="D218" s="2" t="n">
         <v>0</v>
@@ -3697,8 +4802,11 @@
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
-      <c r="B219" s="0" t="s">
-        <v>269</v>
+      <c r="B219" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>0</v>
@@ -3708,8 +4816,11 @@
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
-      <c r="B220" s="0" t="s">
-        <v>270</v>
+      <c r="B220" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>0</v>
@@ -3719,8 +4830,11 @@
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="B221" s="0" t="s">
-        <v>271</v>
+      <c r="B221" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>441</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>0</v>
@@ -3730,8 +4844,11 @@
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
-      <c r="B222" s="0" t="s">
-        <v>272</v>
+      <c r="B222" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>0</v>
@@ -3741,8 +4858,11 @@
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="B223" s="0" t="s">
-        <v>273</v>
+      <c r="B223" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>445</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>0</v>
@@ -3752,8 +4872,11 @@
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
-      <c r="B224" s="0" t="s">
-        <v>274</v>
+      <c r="B224" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>447</v>
       </c>
       <c r="D224" s="2" t="n">
         <v>0</v>
@@ -3763,8 +4886,11 @@
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
-      <c r="B225" s="0" t="s">
-        <v>275</v>
+      <c r="B225" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>449</v>
       </c>
       <c r="D225" s="2" t="n">
         <v>0</v>
@@ -3774,8 +4900,11 @@
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="B226" s="0" t="s">
-        <v>276</v>
+      <c r="B226" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>451</v>
       </c>
       <c r="D226" s="2" t="n">
         <v>0</v>
@@ -3785,8 +4914,11 @@
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
-      <c r="B227" s="0" t="s">
-        <v>277</v>
+      <c r="B227" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>453</v>
       </c>
       <c r="D227" s="2" t="n">
         <v>0</v>
@@ -3796,8 +4928,11 @@
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
-      <c r="B228" s="0" t="s">
-        <v>278</v>
+      <c r="B228" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>455</v>
       </c>
       <c r="D228" s="2" t="n">
         <v>0</v>
@@ -3807,8 +4942,11 @@
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
-      <c r="B229" s="0" t="s">
-        <v>279</v>
+      <c r="B229" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>457</v>
       </c>
       <c r="D229" s="2" t="n">
         <v>0</v>
@@ -3818,8 +4956,11 @@
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
-      <c r="B230" s="0" t="s">
-        <v>280</v>
+      <c r="B230" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>459</v>
       </c>
       <c r="D230" s="2" t="n">
         <v>0</v>
@@ -3829,8 +4970,11 @@
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="B231" s="0" t="s">
-        <v>281</v>
+      <c r="B231" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>461</v>
       </c>
       <c r="D231" s="2" t="n">
         <v>0</v>
@@ -3840,8 +4984,11 @@
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
-      <c r="B232" s="0" t="s">
-        <v>282</v>
+      <c r="B232" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="D232" s="2" t="n">
         <v>0</v>
@@ -3851,8 +4998,11 @@
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="B233" s="0" t="s">
-        <v>283</v>
+      <c r="B233" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>465</v>
       </c>
       <c r="D233" s="2" t="n">
         <v>0</v>
@@ -3862,8 +5012,11 @@
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="B234" s="0" t="s">
-        <v>284</v>
+      <c r="B234" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="D234" s="2" t="n">
         <v>0</v>
@@ -3873,8 +5026,11 @@
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
-      <c r="B235" s="0" t="s">
-        <v>285</v>
+      <c r="B235" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>469</v>
       </c>
       <c r="D235" s="2" t="n">
         <v>0</v>
@@ -3884,8 +5040,11 @@
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="B236" s="0" t="s">
-        <v>286</v>
+      <c r="B236" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="D236" s="2" t="n">
         <v>0</v>
@@ -3895,8 +5054,11 @@
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
-      <c r="B237" s="0" t="s">
-        <v>287</v>
+      <c r="B237" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="D237" s="2" t="n">
         <v>0</v>
@@ -3906,8 +5068,11 @@
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
-      <c r="B238" s="0" t="s">
-        <v>288</v>
+      <c r="B238" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>0</v>
@@ -3917,8 +5082,11 @@
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
-      <c r="B239" s="0" t="s">
-        <v>289</v>
+      <c r="B239" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="D239" s="2" t="n">
         <v>0</v>
@@ -3928,8 +5096,11 @@
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
-      <c r="B240" s="0" t="s">
-        <v>290</v>
+      <c r="B240" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="D240" s="2" t="n">
         <v>0</v>
@@ -3939,8 +5110,11 @@
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="B241" s="0" t="s">
-        <v>291</v>
+      <c r="B241" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>481</v>
       </c>
       <c r="D241" s="2" t="n">
         <v>0</v>
@@ -3950,8 +5124,11 @@
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
-      <c r="B242" s="0" t="s">
-        <v>292</v>
+      <c r="B242" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="D242" s="2" t="n">
         <v>0</v>
@@ -3961,8 +5138,11 @@
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
-      <c r="B243" s="0" t="s">
-        <v>293</v>
+      <c r="B243" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>485</v>
       </c>
       <c r="D243" s="2" t="n">
         <v>0</v>
@@ -3972,8 +5152,11 @@
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
-      <c r="B244" s="0" t="s">
-        <v>294</v>
+      <c r="B244" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>487</v>
       </c>
       <c r="D244" s="2" t="n">
         <v>0</v>
@@ -3983,8 +5166,11 @@
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
-      <c r="B245" s="0" t="s">
-        <v>295</v>
+      <c r="B245" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>489</v>
       </c>
       <c r="D245" s="2" t="n">
         <v>0</v>
@@ -3994,8 +5180,11 @@
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="B246" s="0" t="s">
-        <v>296</v>
+      <c r="B246" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>491</v>
       </c>
       <c r="D246" s="2" t="n">
         <v>0</v>
@@ -4005,8 +5194,11 @@
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
-      <c r="B247" s="0" t="s">
-        <v>297</v>
+      <c r="B247" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>493</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>0</v>
@@ -4016,8 +5208,11 @@
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
-      <c r="B248" s="0" t="s">
-        <v>298</v>
+      <c r="B248" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>495</v>
       </c>
       <c r="D248" s="2" t="n">
         <v>0</v>
@@ -4027,8 +5222,11 @@
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
-      <c r="B249" s="0" t="s">
-        <v>299</v>
+      <c r="B249" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>497</v>
       </c>
       <c r="D249" s="2" t="n">
         <v>0</v>
@@ -4038,8 +5236,11 @@
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
-      <c r="B250" s="0" t="s">
-        <v>300</v>
+      <c r="B250" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D250" s="2" t="n">
         <v>0</v>
@@ -4049,14 +5250,18 @@
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="B251" s="0" t="s">
-        <v>301</v>
+      <c r="B251" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>501</v>
       </c>
       <c r="D251" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C252" s="0"/>
       <c r="D252" s="2"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Sentences/prepared_sentences.xlsx
+++ b/Sentences/prepared_sentences.xlsx
@@ -739,7 +739,7 @@
     <t xml:space="preserve">Co robisz rano?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, RANO, CO, ROBIĆ</t>
+    <t xml:space="preserve">TY, RANO, ROBIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Gdzie jest twój telefon?</t>
@@ -781,7 +781,7 @@
     <t xml:space="preserve">Myślę, że to dobry pomysł.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, MYŚLEĆ, TO, POMYSŁ, DOBRY</t>
+    <t xml:space="preserve">JA, MYŚLEĆ, POMYSŁ, DOBRY</t>
   </si>
   <si>
     <t xml:space="preserve">Czy wiesz, gdzie jest moja książka?</t>
@@ -799,7 +799,7 @@
     <t xml:space="preserve">To jest bardzo ważny dzień w pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">TO, DZIEŃ, BARDZO, WAŻNY, PRACA</t>
+    <t xml:space="preserve">DZIEŃ, BARDZO, WAŻNY, PRACA</t>
   </si>
   <si>
     <t xml:space="preserve">Jestem bardzo zmęczony.</t>
@@ -1027,7 +1027,7 @@
     <t xml:space="preserve">Ile pieniędzy chcesz za ten stary telefon?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, CHCIEĆ, ILE, PIENIĄDZE, TELEFON, STARY, TEN</t>
+    <t xml:space="preserve">TY, CHCIEĆ, ILE, PIENIĄDZE, TELEFON, STARY</t>
   </si>
   <si>
     <t xml:space="preserve">Tata miał wczoraj dużo pieniędzy, więc kupił mi książkę.</t>
@@ -1045,19 +1045,19 @@
     <t xml:space="preserve">Ja dzisiaj nie mam pieniędzy, więc nie mogę kupić tej herbaty.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZISIAJ, JA, PIENIĄDZE, NIE-MIEĆ, WIĘC, HERBATA, TA, KUPIĆ, NIE-MÓC</t>
+    <t xml:space="preserve">DZISIAJ, JA, PIENIĄDZE, NIE-MIEĆ, HERBATA, KUPIĆ, NIE-MÓC</t>
   </si>
   <si>
     <t xml:space="preserve">Mój przyjaciel ma nową pracę, więc dzisiaj jest wesoły.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, PRZYJACIEL, PRACA, NOWA, MIEĆ, WIĘC, DZISIAJ, WESOŁY</t>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL, PRACA, NOWA, MIEĆ, DZISIAJ, WESOŁY</t>
   </si>
   <si>
     <t xml:space="preserve">Ta nowa szkoła zawsze uczy, dlaczego czas to pieniądz.</t>
   </si>
   <si>
-    <t xml:space="preserve">SZKOŁA, NOWA, TA, ZAWSZE, UCZYĆ, DLACZEGO, CZAS, PIENIĄDZ</t>
+    <t xml:space="preserve">SZKOŁA, NOWA, ZAWSZE, UCZYĆ, DLACZEGO, CZAS, PIENIĄDZ</t>
   </si>
   <si>
     <t xml:space="preserve">Mój dobry przyjaciel zawsze wie, kiedy ja jestem smutny.</t>
@@ -1093,7 +1093,7 @@
     <t xml:space="preserve">Jutro będzie nowy dzień, więc my teraz idziemy już spać.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, DZIEŃ, NOWY, WIĘC, TERAZ, MY, SPAĆ, IŚĆ</t>
+    <t xml:space="preserve">JUTRO, DZIEŃ, NOWY, TERAZ, MY, SPAĆ, IŚĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Kiedy mam w domu dużo czasu, bardzo lubię dużo myśleć.</t>
@@ -1177,7 +1177,7 @@
     <t xml:space="preserve">Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, KOBIETA, MĘŻCZYZNA, TEMU, DZIĘKOWAĆ</t>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, KOBIETA, MĘŻCZYZNA, DZIĘKOWAĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Uczymy się dzisiaj, a jutro idziemy spać.</t>
@@ -1201,19 +1201,19 @@
     <t xml:space="preserve">Gdzie mama kupiła tę gorącą kawę?</t>
   </si>
   <si>
-    <t xml:space="preserve">MAMA, GDZIE, KAWA, GORĄCA, TA, KUPIĆ</t>
+    <t xml:space="preserve">MAMA, GDZIE, KAWA, GORĄCA, KUPIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Jak dużo pieniędzy może mieć ta kobieta?</t>
   </si>
   <si>
-    <t xml:space="preserve">KOBIETA, TA, PIENIĄDZE, ILE, MIEĆ, MOŻE</t>
+    <t xml:space="preserve">KOBIETA, PIENIĄDZE, ILE, MIEĆ, MOŻE</t>
   </si>
   <si>
     <t xml:space="preserve">Kocham pić herbatę z babcią i dziadkiem.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, KOCHAĆ, HERBATA, PIĆ, BABCIA, DZIADEK, Z</t>
+    <t xml:space="preserve">JA, KOCHAĆ, HERBATA, PIĆ, BABCIA, DZIADEK</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam, że nie pamiętałem o twoich urodzinach.</t>
@@ -1237,7 +1237,7 @@
     <t xml:space="preserve">Musisz dużo jeść, żeby być zdrowym!</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, MUSIEĆ, JEŚĆ, DUŻO, ZDROWY, BYĆ</t>
+    <t xml:space="preserve">TY, MUSIEĆ, JEŚĆ, DUŻO, ZDROWY</t>
   </si>
   <si>
     <t xml:space="preserve">Czy widzieliście, jak on miga?</t>
@@ -1255,13 +1255,13 @@
     <t xml:space="preserve">Brat często ma dużo czasu dla mamy.</t>
   </si>
   <si>
-    <t xml:space="preserve">BRAT, CZĘSTO, CZAS, DUŻO, MAMA, DLA, MIEĆ</t>
+    <t xml:space="preserve">BRAT, CZĘSTO, CZAS, DUŻO, DLA, MAMA</t>
   </si>
   <si>
     <t xml:space="preserve">Ta kobieta czeka na klucz przy szkole.</t>
   </si>
   <si>
-    <t xml:space="preserve">KOBIETA, TA, SZKOŁA, PRZY, KLUCZ, CZEKAĆ</t>
+    <t xml:space="preserve">KOBIETA, SZKOŁA, KLUCZ, CZEKAĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Zawsze w poniedziałek piję zimną wodę.</t>
@@ -1273,13 +1273,13 @@
     <t xml:space="preserve">Jutro nie mogę pracować, bo jestem bardzo chory.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, JA, PRACOWAĆ, NIE-MÓC, BO, JA, BARDZO, CHORY</t>
+    <t xml:space="preserve">JUTRO, JA, PRACOWAĆ, NIE-MÓC, JA, BARDZO, CHORY</t>
   </si>
   <si>
     <t xml:space="preserve">Ten rok jest dla nas bardzo dobry.</t>
   </si>
   <si>
-    <t xml:space="preserve">ROK, TEN, DLA-NAS, BARDZO, DOBRY</t>
+    <t xml:space="preserve">ROK, DLA-NAS, BARDZO, DOBRY</t>
   </si>
   <si>
     <t xml:space="preserve">Mój przyjaciel zawsze rozumie, co mówię.</t>
@@ -1291,13 +1291,13 @@
     <t xml:space="preserve">Wczoraj dużo myślałem o tej książce.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, JA, MYŚLEĆ, DUŻO, KSIĄŻKA, TA</t>
+    <t xml:space="preserve">WCZORAJ, JA, MYŚLEĆ, DUŻO, TA, KSIĄŻKA</t>
   </si>
   <si>
     <t xml:space="preserve">Dlaczego twój tata kupił taki stary samochód?</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, TATA, DLACZEGO, SAMOCHÓD, STARY, TAKI, KUPIĆ</t>
+    <t xml:space="preserve">TWÓJ, TATA, DLACZEGO, SAMOCHÓD, STARY, KUPIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
@@ -1309,19 +1309,19 @@
     <t xml:space="preserve">To był mój stary telefon.</t>
   </si>
   <si>
-    <t xml:space="preserve">TO, MÓJ, TELEFON, STARY, BYĆ</t>
+    <t xml:space="preserve">MÓJ, TELEFON, STARY, BYĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Dziękuję ci za ten dobry dzień.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZIĘKUJĘ, CI, DZIEŃ, DOBRY, TEN</t>
+    <t xml:space="preserve">DZIĘKUJĘ, CI, DZIEŃ, DOBRY</t>
   </si>
   <si>
     <t xml:space="preserve">Kto ma klucz do domu?</t>
   </si>
   <si>
-    <t xml:space="preserve">KTO, KLUCZ, DOM, DO, MIEĆ</t>
+    <t xml:space="preserve">KTO, KLUCZ, DOM, MIEĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Mężczyzna czekał na ciebie przed szkołą wczoraj rano.</t>
@@ -1357,7 +1357,7 @@
     <t xml:space="preserve">Kiedy masz czas na pracę?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, KIEDY, CZAS, PRACA, NA, MIEĆ</t>
+    <t xml:space="preserve">TY, KIEDY, CZAS, PRACA, MIEĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Ile książek wczoraj kupiłeś?</t>
@@ -1381,7 +1381,7 @@
     <t xml:space="preserve">Dziadek i babcia zawsze mają dla mnie czas.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZIADEK+BABCIA, ZAWSZE, MI, CZAS, MIEĆ</t>
+    <t xml:space="preserve">DZIADEK+BABCIA, ZAWSZE, MI, CZAS</t>
   </si>
   <si>
     <t xml:space="preserve">Ja i mój brat chcemy zostać u kolegi na noc.</t>
@@ -1423,7 +1423,7 @@
     <t xml:space="preserve">On czeka w domu na ciebie i na tatę.</t>
   </si>
   <si>
-    <t xml:space="preserve">ON, DOM, NA-CIEBIE, I, TATA, CZEKAĆ</t>
+    <t xml:space="preserve">ON, DOM, NA-CIEBIE, TATA, CZEKAĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Czy twój pies lubi mojego małego kota?</t>
@@ -1435,7 +1435,7 @@
     <t xml:space="preserve">Ta zimna noc była dla mnie bardzo smutna.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC, ZIMNA, TA, DLA-MNIE, BARDZO, SMUTNA</t>
+    <t xml:space="preserve">NOC, ZIMNA, DLA-MNIE, BARDZO, SMUTNA</t>
   </si>
   <si>
     <t xml:space="preserve">Widzę cię dzisiaj przed moją pracą.</t>
@@ -1453,7 +1453,7 @@
     <t xml:space="preserve">Czy możemy iść do ciebie wieczorem?</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, WIECZÓR, DO-CIEBIE, IŚĆ, MOŻNA</t>
+    <t xml:space="preserve">MY, WIECZÓR, DO-CIEBIE, MOŻNA</t>
   </si>
   <si>
     <t xml:space="preserve">Dziadek zawsze pije gorącą herbatę w nocy.</t>
@@ -1465,7 +1465,7 @@
     <t xml:space="preserve">Kto ci kupił tego psa i kota?</t>
   </si>
   <si>
-    <t xml:space="preserve">KTO, CI, PIES, TEN, I, KOT, KUPIĆ</t>
+    <t xml:space="preserve">KTO, CI, PIES, TEN, KOT, KUPIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam cię za wczoraj.</t>
@@ -1483,7 +1483,7 @@
     <t xml:space="preserve">Mam bardzo dobry pomysł na jutro.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, POMYSŁ, BARDZO, DOBRY, JUTRO, NA, MIEĆ</t>
+    <t xml:space="preserve">JA, MIEĆ, POMYSŁ, BARDZO, DOBRY, JUTRO </t>
   </si>
   <si>
     <t xml:space="preserve">W szkole musimy uczyć się migać.</t>
@@ -1501,7 +1501,7 @@
     <t xml:space="preserve">Gdzie są moje pieniądze z poniedziałku?</t>
   </si>
   <si>
-    <t xml:space="preserve">MOJE, PIENIĄDZE, PONIEDZIAŁEK, Z, GDZIE</t>
+    <t xml:space="preserve">MOJE, PIENIĄDZE, PONIEDZIAŁEK, GDZIE</t>
   </si>
   <si>
     <t xml:space="preserve">Mój tata bardzo kocha mojego brata.</t>
@@ -1600,7 +1600,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1614,10 +1614,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2467,7 +2463,7 @@
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>103</v>
       </c>
       <c r="D52" s="2" t="n">
@@ -2481,7 +2477,7 @@
       <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="3" t="s">
         <v>105</v>
       </c>
       <c r="D53" s="2" t="n">
@@ -2495,7 +2491,7 @@
       <c r="B54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>107</v>
       </c>
       <c r="D54" s="2" t="n">
@@ -2509,7 +2505,7 @@
       <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D55" s="2" t="n">
@@ -2523,7 +2519,7 @@
       <c r="B56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="2" t="n">
@@ -2537,7 +2533,7 @@
       <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>113</v>
       </c>
       <c r="D57" s="2" t="n">
@@ -2551,7 +2547,7 @@
       <c r="B58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D58" s="2" t="n">
@@ -2565,7 +2561,7 @@
       <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D59" s="2" t="n">
@@ -2579,7 +2575,7 @@
       <c r="B60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D60" s="2" t="n">
@@ -2593,7 +2589,7 @@
       <c r="B61" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D61" s="2" t="n">
@@ -2607,7 +2603,7 @@
       <c r="B62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D62" s="2" t="n">
@@ -2621,7 +2617,7 @@
       <c r="B63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D63" s="2" t="n">
@@ -2635,7 +2631,7 @@
       <c r="B64" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D64" s="2" t="n">
@@ -2649,7 +2645,7 @@
       <c r="B65" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D65" s="2" t="n">
@@ -2663,7 +2659,7 @@
       <c r="B66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
         <v>131</v>
       </c>
       <c r="D66" s="2" t="n">
@@ -2677,7 +2673,7 @@
       <c r="B67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D67" s="2" t="n">
@@ -2691,7 +2687,7 @@
       <c r="B68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D68" s="2" t="n">
@@ -2705,7 +2701,7 @@
       <c r="B69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D69" s="2" t="n">
@@ -2719,7 +2715,7 @@
       <c r="B70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D70" s="2" t="n">
@@ -2733,7 +2729,7 @@
       <c r="B71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D71" s="2" t="n">
@@ -2747,7 +2743,7 @@
       <c r="B72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D72" s="2" t="n">
@@ -2761,7 +2757,7 @@
       <c r="B73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D73" s="2" t="n">
@@ -2775,7 +2771,7 @@
       <c r="B74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D74" s="2" t="n">
@@ -2789,7 +2785,7 @@
       <c r="B75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="3" t="s">
         <v>149</v>
       </c>
       <c r="D75" s="2" t="n">
@@ -2803,7 +2799,7 @@
       <c r="B76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D76" s="2" t="n">
@@ -2817,7 +2813,7 @@
       <c r="B77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D77" s="2" t="n">
@@ -2831,7 +2827,7 @@
       <c r="B78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D78" s="2" t="n">
@@ -2845,7 +2841,7 @@
       <c r="B79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D79" s="2" t="n">
@@ -2859,7 +2855,7 @@
       <c r="B80" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="3" t="s">
         <v>159</v>
       </c>
       <c r="D80" s="2" t="n">
@@ -2873,7 +2869,7 @@
       <c r="B81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D81" s="2" t="n">
@@ -2887,7 +2883,7 @@
       <c r="B82" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D82" s="2" t="n">
@@ -2901,7 +2897,7 @@
       <c r="B83" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="3" t="s">
         <v>165</v>
       </c>
       <c r="D83" s="2" t="n">
@@ -2915,7 +2911,7 @@
       <c r="B84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D84" s="2" t="n">
@@ -2929,7 +2925,7 @@
       <c r="B85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="3" t="s">
         <v>169</v>
       </c>
       <c r="D85" s="2" t="n">
@@ -2943,7 +2939,7 @@
       <c r="B86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D86" s="2" t="n">
@@ -2957,7 +2953,7 @@
       <c r="B87" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D87" s="2" t="n">
@@ -2971,7 +2967,7 @@
       <c r="B88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>175</v>
       </c>
       <c r="D88" s="2" t="n">
@@ -2985,7 +2981,7 @@
       <c r="B89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D89" s="2" t="n">
@@ -2999,7 +2995,7 @@
       <c r="B90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="3" t="s">
         <v>179</v>
       </c>
       <c r="D90" s="2" t="n">
@@ -3013,7 +3009,7 @@
       <c r="B91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D91" s="2" t="n">
@@ -3027,7 +3023,7 @@
       <c r="B92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="3" t="s">
         <v>183</v>
       </c>
       <c r="D92" s="2" t="n">
@@ -3041,7 +3037,7 @@
       <c r="B93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D93" s="2" t="n">
@@ -3055,7 +3051,7 @@
       <c r="B94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D94" s="2" t="n">
@@ -3069,7 +3065,7 @@
       <c r="B95" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D95" s="2" t="n">
@@ -3083,7 +3079,7 @@
       <c r="B96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="3" t="s">
         <v>191</v>
       </c>
       <c r="D96" s="2" t="n">
@@ -3097,7 +3093,7 @@
       <c r="B97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="3" t="s">
         <v>193</v>
       </c>
       <c r="D97" s="2" t="n">
@@ -3111,7 +3107,7 @@
       <c r="B98" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D98" s="2" t="n">
@@ -3125,7 +3121,7 @@
       <c r="B99" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>197</v>
       </c>
       <c r="D99" s="2" t="n">
@@ -3139,7 +3135,7 @@
       <c r="B100" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D100" s="2" t="n">
@@ -3153,7 +3149,7 @@
       <c r="B101" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="3" t="s">
         <v>201</v>
       </c>
       <c r="D101" s="2" t="n">
@@ -3167,7 +3163,7 @@
       <c r="B102" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="3" t="s">
         <v>203</v>
       </c>
       <c r="D102" s="2" t="n">
@@ -3181,7 +3177,7 @@
       <c r="B103" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="3" t="s">
         <v>205</v>
       </c>
       <c r="D103" s="2" t="n">
@@ -3195,7 +3191,7 @@
       <c r="B104" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D104" s="2" t="n">
@@ -3209,7 +3205,7 @@
       <c r="B105" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="3" t="s">
         <v>209</v>
       </c>
       <c r="D105" s="2" t="n">
@@ -3223,7 +3219,7 @@
       <c r="B106" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="3" t="s">
         <v>211</v>
       </c>
       <c r="D106" s="2" t="n">
@@ -3237,7 +3233,7 @@
       <c r="B107" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D107" s="2" t="n">
@@ -3251,7 +3247,7 @@
       <c r="B108" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="3" t="s">
         <v>215</v>
       </c>
       <c r="D108" s="2" t="n">
@@ -3265,7 +3261,7 @@
       <c r="B109" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D109" s="2" t="n">
@@ -3279,7 +3275,7 @@
       <c r="B110" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D110" s="2" t="n">
@@ -3293,7 +3289,7 @@
       <c r="B111" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="3" t="s">
         <v>221</v>
       </c>
       <c r="D111" s="2" t="n">
@@ -3307,7 +3303,7 @@
       <c r="B112" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="3" t="s">
         <v>223</v>
       </c>
       <c r="D112" s="2" t="n">
@@ -3321,7 +3317,7 @@
       <c r="B113" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D113" s="2" t="n">
@@ -3335,7 +3331,7 @@
       <c r="B114" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="3" t="s">
         <v>227</v>
       </c>
       <c r="D114" s="2" t="n">
@@ -3349,7 +3345,7 @@
       <c r="B115" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="3" t="s">
         <v>229</v>
       </c>
       <c r="D115" s="2" t="n">
@@ -3363,7 +3359,7 @@
       <c r="B116" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>231</v>
       </c>
       <c r="D116" s="2" t="n">
@@ -3377,7 +3373,7 @@
       <c r="B117" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D117" s="2" t="n">
@@ -3391,7 +3387,7 @@
       <c r="B118" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="3" t="s">
         <v>235</v>
       </c>
       <c r="D118" s="2" t="n">
@@ -3405,7 +3401,7 @@
       <c r="B119" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="3" t="s">
         <v>237</v>
       </c>
       <c r="D119" s="2" t="n">
@@ -3419,7 +3415,7 @@
       <c r="B120" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="3" t="s">
         <v>239</v>
       </c>
       <c r="D120" s="2" t="n">
@@ -3433,7 +3429,7 @@
       <c r="B121" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="3" t="s">
         <v>241</v>
       </c>
       <c r="D121" s="2" t="n">
@@ -3447,7 +3443,7 @@
       <c r="B122" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="3" t="s">
         <v>243</v>
       </c>
       <c r="D122" s="2" t="n">
@@ -3461,7 +3457,7 @@
       <c r="B123" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="3" t="s">
         <v>245</v>
       </c>
       <c r="D123" s="2" t="n">
@@ -3475,7 +3471,7 @@
       <c r="B124" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="3" t="s">
         <v>247</v>
       </c>
       <c r="D124" s="2" t="n">
@@ -3489,7 +3485,7 @@
       <c r="B125" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="3" t="s">
         <v>249</v>
       </c>
       <c r="D125" s="2" t="n">
@@ -3503,7 +3499,7 @@
       <c r="B126" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="3" t="s">
         <v>251</v>
       </c>
       <c r="D126" s="2" t="n">
@@ -3517,7 +3513,7 @@
       <c r="B127" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D127" s="2" t="n">
@@ -3531,7 +3527,7 @@
       <c r="B128" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="3" t="s">
         <v>255</v>
       </c>
       <c r="D128" s="2" t="n">
@@ -3545,7 +3541,7 @@
       <c r="B129" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="3" t="s">
         <v>257</v>
       </c>
       <c r="D129" s="2" t="n">
@@ -3559,7 +3555,7 @@
       <c r="B130" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="3" t="s">
         <v>259</v>
       </c>
       <c r="D130" s="2" t="n">
@@ -3573,7 +3569,7 @@
       <c r="B131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D131" s="2" t="n">
@@ -3587,7 +3583,7 @@
       <c r="B132" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D132" s="2" t="n">
@@ -3601,7 +3597,7 @@
       <c r="B133" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="3" t="s">
         <v>265</v>
       </c>
       <c r="D133" s="2" t="n">
@@ -3615,7 +3611,7 @@
       <c r="B134" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="3" t="s">
         <v>267</v>
       </c>
       <c r="D134" s="2" t="n">
@@ -3629,7 +3625,7 @@
       <c r="B135" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="3" t="s">
         <v>269</v>
       </c>
       <c r="D135" s="2" t="n">
@@ -3643,7 +3639,7 @@
       <c r="B136" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="3" t="s">
         <v>271</v>
       </c>
       <c r="D136" s="2" t="n">
@@ -3657,7 +3653,7 @@
       <c r="B137" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="3" t="s">
         <v>273</v>
       </c>
       <c r="D137" s="2" t="n">
@@ -3671,7 +3667,7 @@
       <c r="B138" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="3" t="s">
         <v>275</v>
       </c>
       <c r="D138" s="2" t="n">
@@ -3685,7 +3681,7 @@
       <c r="B139" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="3" t="s">
         <v>277</v>
       </c>
       <c r="D139" s="2" t="n">
@@ -3699,7 +3695,7 @@
       <c r="B140" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="3" t="s">
         <v>279</v>
       </c>
       <c r="D140" s="2" t="n">
@@ -3713,7 +3709,7 @@
       <c r="B141" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="3" t="s">
         <v>281</v>
       </c>
       <c r="D141" s="2" t="n">
@@ -3727,7 +3723,7 @@
       <c r="B142" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="3" t="s">
         <v>283</v>
       </c>
       <c r="D142" s="2" t="n">
@@ -3741,7 +3737,7 @@
       <c r="B143" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="3" t="s">
         <v>285</v>
       </c>
       <c r="D143" s="2" t="n">
@@ -3755,7 +3751,7 @@
       <c r="B144" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="3" t="s">
         <v>287</v>
       </c>
       <c r="D144" s="2" t="n">
@@ -3769,7 +3765,7 @@
       <c r="B145" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="3" t="s">
         <v>289</v>
       </c>
       <c r="D145" s="2" t="n">
@@ -3783,7 +3779,7 @@
       <c r="B146" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="3" t="s">
         <v>291</v>
       </c>
       <c r="D146" s="2" t="n">
@@ -3797,7 +3793,7 @@
       <c r="B147" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="3" t="s">
         <v>293</v>
       </c>
       <c r="D147" s="2" t="n">
@@ -3811,7 +3807,7 @@
       <c r="B148" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="3" t="s">
         <v>295</v>
       </c>
       <c r="D148" s="2" t="n">
@@ -3825,7 +3821,7 @@
       <c r="B149" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="3" t="s">
         <v>297</v>
       </c>
       <c r="D149" s="2" t="n">
@@ -3839,7 +3835,7 @@
       <c r="B150" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="3" t="s">
         <v>299</v>
       </c>
       <c r="D150" s="2" t="n">
@@ -3853,7 +3849,7 @@
       <c r="B151" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="3" t="s">
         <v>301</v>
       </c>
       <c r="D151" s="2" t="n">
@@ -3867,7 +3863,7 @@
       <c r="B152" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="3" t="s">
         <v>303</v>
       </c>
       <c r="D152" s="2" t="n">
@@ -3881,7 +3877,7 @@
       <c r="B153" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" s="3" t="s">
         <v>305</v>
       </c>
       <c r="D153" s="2" t="n">
@@ -3895,7 +3891,7 @@
       <c r="B154" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" s="3" t="s">
         <v>307</v>
       </c>
       <c r="D154" s="2" t="n">
@@ -3909,7 +3905,7 @@
       <c r="B155" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="3" t="s">
         <v>309</v>
       </c>
       <c r="D155" s="2" t="n">
@@ -3923,7 +3919,7 @@
       <c r="B156" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="3" t="s">
         <v>311</v>
       </c>
       <c r="D156" s="2" t="n">
@@ -3937,7 +3933,7 @@
       <c r="B157" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="3" t="s">
         <v>313</v>
       </c>
       <c r="D157" s="2" t="n">
@@ -3951,7 +3947,7 @@
       <c r="B158" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="3" t="s">
         <v>315</v>
       </c>
       <c r="D158" s="2" t="n">
@@ -3965,7 +3961,7 @@
       <c r="B159" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="3" t="s">
         <v>317</v>
       </c>
       <c r="D159" s="2" t="n">
@@ -3979,7 +3975,7 @@
       <c r="B160" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="3" t="s">
         <v>319</v>
       </c>
       <c r="D160" s="2" t="n">
@@ -3993,7 +3989,7 @@
       <c r="B161" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="3" t="s">
         <v>321</v>
       </c>
       <c r="D161" s="2" t="n">
@@ -4007,7 +4003,7 @@
       <c r="B162" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="3" t="s">
         <v>323</v>
       </c>
       <c r="D162" s="2" t="n">
@@ -4021,7 +4017,7 @@
       <c r="B163" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="3" t="s">
         <v>325</v>
       </c>
       <c r="D163" s="2" t="n">
@@ -4035,7 +4031,7 @@
       <c r="B164" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="3" t="s">
         <v>327</v>
       </c>
       <c r="D164" s="2" t="n">
@@ -4049,7 +4045,7 @@
       <c r="B165" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="3" t="s">
         <v>329</v>
       </c>
       <c r="D165" s="2" t="n">
@@ -4063,7 +4059,7 @@
       <c r="B166" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="3" t="s">
         <v>331</v>
       </c>
       <c r="D166" s="2" t="n">
@@ -4077,7 +4073,7 @@
       <c r="B167" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="3" t="s">
         <v>333</v>
       </c>
       <c r="D167" s="2" t="n">
@@ -4091,7 +4087,7 @@
       <c r="B168" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="3" t="s">
         <v>335</v>
       </c>
       <c r="D168" s="2" t="n">
@@ -4105,7 +4101,7 @@
       <c r="B169" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="3" t="s">
         <v>337</v>
       </c>
       <c r="D169" s="2" t="n">
@@ -4119,7 +4115,7 @@
       <c r="B170" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="3" t="s">
         <v>339</v>
       </c>
       <c r="D170" s="2" t="n">
@@ -4133,7 +4129,7 @@
       <c r="B171" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="3" t="s">
         <v>341</v>
       </c>
       <c r="D171" s="2" t="n">
@@ -4147,7 +4143,7 @@
       <c r="B172" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" s="3" t="s">
         <v>343</v>
       </c>
       <c r="D172" s="2" t="n">
@@ -4161,7 +4157,7 @@
       <c r="B173" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" s="3" t="s">
         <v>345</v>
       </c>
       <c r="D173" s="2" t="n">
@@ -4175,7 +4171,7 @@
       <c r="B174" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" s="3" t="s">
         <v>347</v>
       </c>
       <c r="D174" s="2" t="n">
@@ -4189,7 +4185,7 @@
       <c r="B175" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" s="3" t="s">
         <v>349</v>
       </c>
       <c r="D175" s="2" t="n">
@@ -4203,7 +4199,7 @@
       <c r="B176" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="3" t="s">
         <v>351</v>
       </c>
       <c r="D176" s="2" t="n">
@@ -4217,7 +4213,7 @@
       <c r="B177" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="3" t="s">
         <v>353</v>
       </c>
       <c r="D177" s="2" t="n">
@@ -4231,7 +4227,7 @@
       <c r="B178" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" s="3" t="s">
         <v>355</v>
       </c>
       <c r="D178" s="2" t="n">
@@ -4245,7 +4241,7 @@
       <c r="B179" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D179" s="2" t="n">
@@ -4259,7 +4255,7 @@
       <c r="B180" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" s="3" t="s">
         <v>359</v>
       </c>
       <c r="D180" s="2" t="n">
@@ -4273,7 +4269,7 @@
       <c r="B181" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="3" t="s">
         <v>361</v>
       </c>
       <c r="D181" s="2" t="n">
@@ -4287,7 +4283,7 @@
       <c r="B182" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="3" t="s">
         <v>363</v>
       </c>
       <c r="D182" s="2" t="n">
@@ -4301,7 +4297,7 @@
       <c r="B183" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" s="3" t="s">
         <v>365</v>
       </c>
       <c r="D183" s="2" t="n">
@@ -4315,7 +4311,7 @@
       <c r="B184" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" s="3" t="s">
         <v>367</v>
       </c>
       <c r="D184" s="2" t="n">
@@ -4329,7 +4325,7 @@
       <c r="B185" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" s="3" t="s">
         <v>369</v>
       </c>
       <c r="D185" s="2" t="n">
@@ -4343,7 +4339,7 @@
       <c r="B186" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" s="3" t="s">
         <v>371</v>
       </c>
       <c r="D186" s="2" t="n">
@@ -4357,7 +4353,7 @@
       <c r="B187" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C187" s="3" t="s">
         <v>373</v>
       </c>
       <c r="D187" s="2" t="n">
@@ -4371,7 +4367,7 @@
       <c r="B188" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" s="3" t="s">
         <v>375</v>
       </c>
       <c r="D188" s="2" t="n">
@@ -4385,7 +4381,7 @@
       <c r="B189" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C189" s="4" t="s">
+      <c r="C189" s="3" t="s">
         <v>377</v>
       </c>
       <c r="D189" s="2" t="n">
@@ -4399,7 +4395,7 @@
       <c r="B190" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" s="3" t="s">
         <v>379</v>
       </c>
       <c r="D190" s="2" t="n">
@@ -4413,7 +4409,7 @@
       <c r="B191" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="3" t="s">
         <v>381</v>
       </c>
       <c r="D191" s="2" t="n">
@@ -4427,7 +4423,7 @@
       <c r="B192" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C192" s="3" t="s">
         <v>383</v>
       </c>
       <c r="D192" s="2" t="n">
@@ -4441,7 +4437,7 @@
       <c r="B193" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C193" s="3" t="s">
         <v>385</v>
       </c>
       <c r="D193" s="2" t="n">
@@ -4455,7 +4451,7 @@
       <c r="B194" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D194" s="2" t="n">
@@ -4469,7 +4465,7 @@
       <c r="B195" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" s="3" t="s">
         <v>389</v>
       </c>
       <c r="D195" s="2" t="n">
@@ -4483,7 +4479,7 @@
       <c r="B196" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" s="3" t="s">
         <v>391</v>
       </c>
       <c r="D196" s="2" t="n">
@@ -4497,7 +4493,7 @@
       <c r="B197" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" s="3" t="s">
         <v>393</v>
       </c>
       <c r="D197" s="2" t="n">
@@ -4511,7 +4507,7 @@
       <c r="B198" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" s="3" t="s">
         <v>395</v>
       </c>
       <c r="D198" s="2" t="n">
@@ -4525,7 +4521,7 @@
       <c r="B199" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" s="3" t="s">
         <v>397</v>
       </c>
       <c r="D199" s="2" t="n">
@@ -4539,7 +4535,7 @@
       <c r="B200" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" s="3" t="s">
         <v>399</v>
       </c>
       <c r="D200" s="2" t="n">
@@ -4553,7 +4549,7 @@
       <c r="B201" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" s="3" t="s">
         <v>401</v>
       </c>
       <c r="D201" s="2" t="n">
@@ -4567,7 +4563,7 @@
       <c r="B202" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" s="3" t="s">
         <v>403</v>
       </c>
       <c r="D202" s="2" t="n">
@@ -4581,7 +4577,7 @@
       <c r="B203" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D203" s="2" t="n">
@@ -4595,7 +4591,7 @@
       <c r="B204" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" s="3" t="s">
         <v>407</v>
       </c>
       <c r="D204" s="2" t="n">
@@ -4609,7 +4605,7 @@
       <c r="B205" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" s="3" t="s">
         <v>409</v>
       </c>
       <c r="D205" s="2" t="n">
@@ -4623,7 +4619,7 @@
       <c r="B206" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="3" t="s">
         <v>411</v>
       </c>
       <c r="D206" s="2" t="n">
@@ -4637,7 +4633,7 @@
       <c r="B207" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" s="3" t="s">
         <v>413</v>
       </c>
       <c r="D207" s="2" t="n">
@@ -4651,7 +4647,7 @@
       <c r="B208" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" s="3" t="s">
         <v>415</v>
       </c>
       <c r="D208" s="2" t="n">
@@ -4665,7 +4661,7 @@
       <c r="B209" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" s="3" t="s">
         <v>417</v>
       </c>
       <c r="D209" s="2" t="n">
@@ -4679,7 +4675,7 @@
       <c r="B210" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" s="3" t="s">
         <v>419</v>
       </c>
       <c r="D210" s="2" t="n">
@@ -4693,7 +4689,7 @@
       <c r="B211" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D211" s="2" t="n">
@@ -4707,7 +4703,7 @@
       <c r="B212" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" s="3" t="s">
         <v>423</v>
       </c>
       <c r="D212" s="2" t="n">
@@ -4721,7 +4717,7 @@
       <c r="B213" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" s="3" t="s">
         <v>425</v>
       </c>
       <c r="D213" s="2" t="n">
@@ -4735,7 +4731,7 @@
       <c r="B214" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D214" s="2" t="n">
@@ -4749,7 +4745,7 @@
       <c r="B215" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="3" t="s">
         <v>429</v>
       </c>
       <c r="D215" s="2" t="n">
@@ -4763,7 +4759,7 @@
       <c r="B216" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" s="3" t="s">
         <v>431</v>
       </c>
       <c r="D216" s="2" t="n">
@@ -4777,7 +4773,7 @@
       <c r="B217" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C217" s="3" t="s">
         <v>433</v>
       </c>
       <c r="D217" s="2" t="n">
@@ -4791,7 +4787,7 @@
       <c r="B218" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C218" s="3" t="s">
         <v>435</v>
       </c>
       <c r="D218" s="2" t="n">
@@ -4805,7 +4801,7 @@
       <c r="B219" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="C219" s="3" t="s">
         <v>437</v>
       </c>
       <c r="D219" s="2" t="n">
@@ -4819,7 +4815,7 @@
       <c r="B220" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" s="3" t="s">
         <v>439</v>
       </c>
       <c r="D220" s="2" t="n">
@@ -4833,7 +4829,7 @@
       <c r="B221" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" s="3" t="s">
         <v>441</v>
       </c>
       <c r="D221" s="2" t="n">
@@ -4847,7 +4843,7 @@
       <c r="B222" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C222" s="4" t="s">
+      <c r="C222" s="3" t="s">
         <v>443</v>
       </c>
       <c r="D222" s="2" t="n">
@@ -4861,7 +4857,7 @@
       <c r="B223" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C223" s="3" t="s">
         <v>445</v>
       </c>
       <c r="D223" s="2" t="n">
@@ -4875,7 +4871,7 @@
       <c r="B224" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C224" s="4" t="s">
+      <c r="C224" s="3" t="s">
         <v>447</v>
       </c>
       <c r="D224" s="2" t="n">
@@ -4889,7 +4885,7 @@
       <c r="B225" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C225" s="4" t="s">
+      <c r="C225" s="3" t="s">
         <v>449</v>
       </c>
       <c r="D225" s="2" t="n">
@@ -4903,7 +4899,7 @@
       <c r="B226" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C226" s="3" t="s">
         <v>451</v>
       </c>
       <c r="D226" s="2" t="n">
@@ -4917,7 +4913,7 @@
       <c r="B227" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="C227" s="3" t="s">
         <v>453</v>
       </c>
       <c r="D227" s="2" t="n">
@@ -4931,7 +4927,7 @@
       <c r="B228" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C228" s="4" t="s">
+      <c r="C228" s="3" t="s">
         <v>455</v>
       </c>
       <c r="D228" s="2" t="n">
@@ -4945,7 +4941,7 @@
       <c r="B229" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="C229" s="3" t="s">
         <v>457</v>
       </c>
       <c r="D229" s="2" t="n">
@@ -4959,7 +4955,7 @@
       <c r="B230" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C230" s="3" t="s">
         <v>459</v>
       </c>
       <c r="D230" s="2" t="n">
@@ -4973,7 +4969,7 @@
       <c r="B231" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="C231" s="3" t="s">
         <v>461</v>
       </c>
       <c r="D231" s="2" t="n">
@@ -4987,7 +4983,7 @@
       <c r="B232" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C232" s="3" t="s">
         <v>463</v>
       </c>
       <c r="D232" s="2" t="n">
@@ -5001,7 +4997,7 @@
       <c r="B233" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C233" s="4" t="s">
+      <c r="C233" s="3" t="s">
         <v>465</v>
       </c>
       <c r="D233" s="2" t="n">
@@ -5015,7 +5011,7 @@
       <c r="B234" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C234" s="4" t="s">
+      <c r="C234" s="3" t="s">
         <v>467</v>
       </c>
       <c r="D234" s="2" t="n">
@@ -5029,7 +5025,7 @@
       <c r="B235" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="C235" s="3" t="s">
         <v>469</v>
       </c>
       <c r="D235" s="2" t="n">
@@ -5043,7 +5039,7 @@
       <c r="B236" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C236" s="3" t="s">
         <v>471</v>
       </c>
       <c r="D236" s="2" t="n">
@@ -5057,7 +5053,7 @@
       <c r="B237" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="C237" s="3" t="s">
         <v>473</v>
       </c>
       <c r="D237" s="2" t="n">
@@ -5071,7 +5067,7 @@
       <c r="B238" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C238" s="3" t="s">
         <v>475</v>
       </c>
       <c r="D238" s="2" t="n">
@@ -5085,7 +5081,7 @@
       <c r="B239" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="C239" s="3" t="s">
         <v>477</v>
       </c>
       <c r="D239" s="2" t="n">
@@ -5099,7 +5095,7 @@
       <c r="B240" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C240" s="4" t="s">
+      <c r="C240" s="3" t="s">
         <v>479</v>
       </c>
       <c r="D240" s="2" t="n">
@@ -5113,7 +5109,7 @@
       <c r="B241" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C241" s="4" t="s">
+      <c r="C241" s="3" t="s">
         <v>481</v>
       </c>
       <c r="D241" s="2" t="n">
@@ -5127,7 +5123,7 @@
       <c r="B242" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C242" s="4" t="s">
+      <c r="C242" s="3" t="s">
         <v>483</v>
       </c>
       <c r="D242" s="2" t="n">
@@ -5141,7 +5137,7 @@
       <c r="B243" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" s="3" t="s">
         <v>485</v>
       </c>
       <c r="D243" s="2" t="n">
@@ -5155,7 +5151,7 @@
       <c r="B244" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C244" s="3" t="s">
         <v>487</v>
       </c>
       <c r="D244" s="2" t="n">
@@ -5169,7 +5165,7 @@
       <c r="B245" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="C245" s="3" t="s">
         <v>489</v>
       </c>
       <c r="D245" s="2" t="n">
@@ -5183,7 +5179,7 @@
       <c r="B246" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" s="3" t="s">
         <v>491</v>
       </c>
       <c r="D246" s="2" t="n">
@@ -5197,7 +5193,7 @@
       <c r="B247" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" s="3" t="s">
         <v>493</v>
       </c>
       <c r="D247" s="2" t="n">
@@ -5211,7 +5207,7 @@
       <c r="B248" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="C248" s="3" t="s">
         <v>495</v>
       </c>
       <c r="D248" s="2" t="n">
@@ -5225,7 +5221,7 @@
       <c r="B249" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" s="3" t="s">
         <v>497</v>
       </c>
       <c r="D249" s="2" t="n">
@@ -5239,7 +5235,7 @@
       <c r="B250" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" s="3" t="s">
         <v>499</v>
       </c>
       <c r="D250" s="2" t="n">
@@ -5253,7 +5249,7 @@
       <c r="B251" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" s="3" t="s">
         <v>501</v>
       </c>
       <c r="D251" s="2" t="n">
@@ -5261,7 +5257,6 @@
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C252" s="0"/>
       <c r="D252" s="2"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Sentences/prepared_sentences.xlsx
+++ b/Sentences/prepared_sentences.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="751">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -31,9 +31,6 @@
     <t xml:space="preserve">Kolejność znaków </t>
   </si>
   <si>
-    <t xml:space="preserve">Ilość</t>
-  </si>
-  <si>
     <t xml:space="preserve">Babcia i dziadek mają stary samochód.</t>
   </si>
   <si>
@@ -1526,6 +1523,756 @@
   </si>
   <si>
     <t xml:space="preserve">JUTRO, MY, DOM, STARY, DZIADEK, ZOSTAĆ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile czasu masz dzisiaj na tę książkę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy to jest ten nowy telefon z mojej pracy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wesoły mężczyzna kupił małego psa i kota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie pamiętam, kiedy ty pracowałeś w poniedziałek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myślę, że on będzie bardzo chory jutro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To jest bardzo wesoły dzień dla nas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego jesteś dla mnie taki zimny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostałem przed szkołą, bo czekałem na babcię.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę być dobrym przyjacielem dla ciebie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy słyszycie tego kota przed szkołą?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja wczoraj w nocy myślałem o mojej pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, mój ważny klucz już został u taty w samochodzie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy ty idziesz do domu, ja idę spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uczę się migać w poniedziałek po szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupiłem dla ciebie dużo książek na urodziny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze wesoła siostra już bardzo lubi pracować rano w środę i w czwartek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wiesz, jak kupić ten duży dom?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, gdzie jest woda dla małego psa, który jest chory? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem widziałam mojego starego kolegę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niech ten pies zostanie w domu z kotem!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wy rozumiecie, że jutro będzie bardzo zimny i smutny dzień dla mamy? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piję teraz herbatę w tę środę, bo często w taki gorący dzień musimy dużo pić. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy masz dla mnie nowy pomysł na urodziny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praca w noc nie jest dobra dla mnie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia zawsze kocha mojego małego brata.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty nie masz dla mnie czasu, żeby mówić.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ona wczoraj bardzo dużo jadła?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój telefon jest mały, a twój samochód jest duży.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro z tobą idę po herbatę, bo to taki zdrowy pomysł na ten zimny wtorek. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że nie mogę ci dzisiaj pomóc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Będę ci dziękować, że on chce dzisiaj być.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętaj, żeby jeść dużo i pić dużo wody.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętam, żeby zawsze dziękować za dobrą pracę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten rok to czas, kiedy już bardzo dużo pracujemy w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brat ma ten nowy telefon już rok i jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Już od roku zawsze rano lubię pić gorącą wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy on wczoraj kupił tego małego kota?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wiesz, dlaczego twoja siostra jest dzisiaj smutna?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziadek, który jest chory, już rok nie był w szkole </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W poniedziałek wieczorem będę na ciebie czekać przed domem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty nie rozumiesz, że ja jestem zmęczony i muszę teraz dużo spać. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobiety lubią gorącą herbatę, a mężczyźni zimną wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem kupiłem nową książkę dla chorej mamy na jej urodziny. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój kolega z pracy ma dzisiaj urodziny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję, że pomogłeś mojemu psu wczoraj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile w roku się to robi, żeby być zdrowym? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja nie mam teraz pieniędzy na tę dużą książkę dla siostry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ten mężczyzna z psem idzie do szkoły?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W nocy kot mojego brata bardzo często pije wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie pamiętam, o czym ty do mnie mówiłeś rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostań u nas na herbatę we wtorek </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że wczoraj rano nie było mnie w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy twój mały brat lubi się uczyć?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętaj, żeby rano kupić gorącą kawę dla dziadka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My bardzo często myślimy o twoim nowym pomyśle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ty zawsze musisz być taki zmęczony?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widziałem wczoraj twoją babcię w starym samochodzie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę wiedzieć, kto ma ten klucz od domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesteś bardzo zdrowy, bo nie jesz w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W środę i w czwartek to jest ważny klucz. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, czy wy w środę to robicie? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czekam, żeby z tobą iść na kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy zdrowym jest robić to z roku na rok, i ile? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uczę się dużo, żeby móc pracować w szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy kupisz ten stary dom dla dziadka?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woda w noc była bardzo zimna dla mojego psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze w poniedziałek rano jestem bardzo wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kocham moją mamę i mojego tatę za ten nowy dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój pies zawsze chce dużo jeść rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mężczyzna czekał pod domem, żeby mi pomóc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty dobrze wiesz, jak kupić taki samochód bez pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj w nocy myślałem, żeby kupić dużego kota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia robiła gorącą herbatę dla ciebie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie jest ten mały kot mojej siostry?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano idę do szkoły z moim nowym telefonem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, ile mogę to robić w czwartek? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praca w domu jest dla mnie bardzo dobra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze pamiętam o twoich urodzinach w poniedziałek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę kupić dla ciebie książkę, żebyś nie był smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wy rozumiecie, że to był ważny rok? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja i ty musimy dużo pracować, żeby mieć na dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto wczoraj rano kupił ten stary samochód taty?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile to się robi, rok? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego jesteś bardzo zimny w ten gorący dzień?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobieta z małym psem idzie rano do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że nie mam czasu dla ich siostry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Często słyszę tego psa przed moją pracą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem byłem u kolegi w starym domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój nowy pomysł na pracę jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy idziemy na dużą kawę z kolegą?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niech mój przyjaciel czeka na mnie przed szkołą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze myślę o tym, żeby być wesołym i zdrowym.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My chcemy kupić ten stary samochód w poniedziałek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My jesteśmy dobrymi przyjacielami od wczoraj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro będę chory, bo nie śpię w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję ci za tę książkę o starym domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie jest klucz do tego małego samochodu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja bardzo lubię, kiedy pijesz ze mną kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty wczoraj mówiłeś, że nie masz pieniędzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jego tata kupił telefon dla mojej nowej szkoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj rano widziałem, jak ten mężczyzna miga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia i dziadek piją gorącą wodę rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jej kot bardzo często śpi na tej dużej książce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze pamiętam, żeby pić wodę przed pracą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro wieczorem idę do ciebie bez psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty nie rozumiesz, jak bardzo jestem zmęczony w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie my wczoraj kupiliśmy tę gorącą kawę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto chory idzie rano do szkoły?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich brat ma urodziny w poniedziałek wieczorem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile kawy dzisiaj rano piła twoja mama?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czekam na ciebie, żeby iść do starych przyjaciół.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy ty widziałeś rano mojego małego brata?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj bardzo chcę uczyć się z twoją siostrą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mężczyzna bez samochodu idzie do pracy w nocy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ta książka, którą ma ta kobieta, jest dla ciebie taka ważna?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten dzień był dla mojego przyjaciela bardzo smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty zawsze myślisz, że ich dom jest twój.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziadek nie słyszy, co babcia do niego mówi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myślę, że twój pomysł na urodziny jest wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostań u dziadka na noc, bo jesteś zmęczony.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czekam na ten ważny dla mnie czas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam klucza, więc muszę czekać na tatę przed domem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wiesz, gdzie brat mojego kolegi kupił telefon?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kocham ten czas, kiedy rano we wtorek piję kawę</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kup małego kota, nie tego starego psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jej mały pies wczoraj w nocy jadł książkę taty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętam, że mam rano iść do szkoły z jego małym przyjacielem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze myślę o mojej starej szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jej brat kupił wczoraj dla mnie nowy telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten wesoły pies często śpi u mnie w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano będę pracować z twoim przyjacielem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam dzisiaj czasu na kawę z tobą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wy już wiecie, co on chce robić w ten czwartek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego myślisz, że jestem bardzo smutny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy kupiłeś ten duży dom dla dziadka?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój stary samochód nie chce rano pracować.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję ci za ten telefon, który kupiłeś na moje urodziny w czwartek. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie twój kolega kupił taką dobrą herbatę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W poniedziałek wieczorem będę dużo pracował u mamy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy widziałeś rano mojego psa przed domem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętaj, żeby uczyć się w domu w dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty zawsze masz czas, żeby pić ze mną herbatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W nocy słyszałem, jak ten kot dużo pije.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesteś dzisiaj zmęczony, bo wczoraj dużo pracowałeś.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój tata nie lubi, kiedy pije gorącą wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My bardzo często pijemy kawę u twojej siostry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ta mała książka jest dla ciebie ważna?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie wczoraj uczyłeś się migać z moim bratem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chcę kupić stary dom z dużym psem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie rozumiem, o czym ty do mnie rano mówiłeś.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj nie mogę iść do pracy, bo chory brat jest w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czekam na moje pieniądze od poniedziałku.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem widziałem, jak twój kolega pije kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia lubi, żeby kot spał rano pod domem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten czas był dla mojego przyjaciela bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kocham ten wesoły dzień w szkole z moim bratem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego nie pamiętasz o moich urodzinach w poniedziałek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siostra jest często zmęczona.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niech ta kobieta zostanie u ciebie na herbatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze rano dziękuję tacie za dobrą pracę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W nocy mój dziadek nie słyszy, co babcia mówi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do pracy z psem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój telefon był wczoraj rano w moim starym samochodzie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam klucza, żeby być rano w domu u dziadka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja będę na ciebie czekać z gorącą wodą rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mama musi teraz jeść.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie jest woda dla mojego nowego psa i kota?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj w nocy myślałem, co dzisiaj robić w szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano kupię dla ciebie ten stary samochód taty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy twój przyjaciel ma czas na kawę po pracy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Będziemy uczyć się migać o mojej starej pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostań z bratem w domu, bo on jest smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja i ty musimy dużo pić, żeby nie być zmęczonymi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój nowy dom w poniedziałek rano jest bardzo zimny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego ten stary kot zawsze dużo je u babci?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mężczyzna czekał rano z psem, żeby iść do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że wczoraj rano kupiłem ten nowy telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Często słyszę mojego psa rano, kiedy idę do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem byłem z małym psem w starym domu dziadka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My chcemy dużo spać, żeby nie być chorym rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No to ile będziesz to robić? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niech mój przyjaciel czeka na ciebie rano u dziadka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy to jest środa, czy czwartek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój wesoły tata wczoraj pił z moim dziadkiem wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My chcemy wiedzieć, gdzie wczoraj był twój samochód rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro w nocy będę spać u brata z psem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiedy kupisz dla mnie tę książkę o starym domu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja bardzo lubię pić z tobą dobrą gorącą herbatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie my wczoraj widzieliśmy ten stary samochód mojego przyjaciela?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, ale to był taki ważny rok, czy wy to teraz rozumiecie?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój dziadek w poniedziałek wieczorem był zmęczony i smutny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mogę dzisiaj iść po kawę z moim nowym przyjacielem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babcia i dziadek dzisiaj rano pili ze mną wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój brat zawsze bardzo lubi mówić rano o pracy w środę?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile to było robione? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętam, żeby pić zimną wodę w gorący dzień.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro rano idę z małym psem do ciebie po klucz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ty nie pamiętasz, dlaczego wczoraj byłem u ciebie z bratem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile kawy dzisiaj pijesz, żeby mieć na to czas?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto wesoły i zdrowy idzie z moim bratem do starej szkoły?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój stary pies ma dzisiaj urodziny rano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czekam rano przed twoim nowym domem z gorącą herbatą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzisiaj rano chcę uczyć się migać z twoją babcią.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To było we wtorek i w środę, teraz już to rozumiem, to był taki ważny rok. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wy się teraz kochacie, czy to już taki nowy pomysł na ten czwartek? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziadek nie słyszy, kiedy babcia mówi do kota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj w nocy myślałem o tej książce z moim bratem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zostań rano w domu u dziadka, bo jesteś bardzo chory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie mam rano klucza od twojego starego samochodu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy wiesz, co ten duży pies jadł w poniedziałek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kocham ten czas rano, kiedy kot śpi u mnie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj wieczorem widziałem mojego psa przed szkołą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętam, żeby dużo pracować i mieć pieniądze na nowy dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten bardzo smutny mężczyzna nie lubi pić ze mną kawy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie wczoraj kupiłeś tę książkę dla przyjaciela?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój tata bardzo kocha rano pić herbatę z wesołym psem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze chcę być z tobą rano u ciebie w pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twój pomysł na urodziny brata w poniedziałek jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niech kot zostanie u ciebie z moim starym tatą.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do nowej szkoły rano?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj rano mój tata kupił ten stary dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego zawsze pijesz gorącą wodę z mamą?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We wtorek rano mój brat musi iść do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W środę ja i ty chcemy kupić nowy dom, który będzie dla nas ważny </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy w czwartek twój pies był chory i kto mu pomógł? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dlaczego we wtorek zawsze jesteś smutny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W środę wieczorem dziadek pije gorącą herbatę, bo kocha ten zdrowy pomysł. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Już pamiętam że mój przyjaciel ma urodziny w czwartek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wczoraj był poniedziałek, a dzisiaj jest wtorek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kto musi pracować w środę w nocy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W czwartek rano babcia czeka na mój telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobieta i mężczyzna idą do szkoły we wtorek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja wiem, że w środę będę bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W czwartek siostra chce mieć nową książkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdzie ty byłeś we wtorek rano?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mój stary kot lubi spać w środę w domu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile pieniędzy musisz mieć na czwartek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We wtorek my nie mamy czasu na kawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawsze w środę uczę się migać, teraz już kocham to robić. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W czwartek wieczorem twój kolega jest wesoły.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pamiętam, co mój tata mówił we wtorek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W środę ten duży samochód jest mój, a wy go już kochacie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziękuję, że chcesz mi pomóc w czwartek, to taki zdrowy pomysł. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak bardzo lubisz ten wtorek?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W środę rano muszę pić zimną wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jutro czwartek, więc idę do pracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przepraszam, że nie byłem zdrowy we wtorek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teraz idę do pracy, bo muszę iść po klucz, który ma moja siostra. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On się teraz uczy, żeby rozumieć, jak pomóc chorej kobiecie. </t>
   </si>
 </sst>
 </file>
@@ -1546,16 +2293,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1740,11 +2490,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D501"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="84.29"/>
   </cols>
   <sheetData>
@@ -1758,3661 +2508,5059 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D107" s="2"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D108" s="2"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D109" s="2"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D110" s="2"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D111" s="2"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D112" s="2"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D113" s="2"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D114" s="2"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D115" s="2"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D116" s="2"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D117" s="2"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D118" s="2"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D119" s="2"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D120" s="2"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D121" s="2"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D122" s="2"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C123" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D123" s="2"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D124" s="2"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C125" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D125" s="2"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D126" s="2"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D127" s="2"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D128" s="2"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D129" s="2"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C130" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D130" s="2"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D131" s="2"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D132" s="2"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D133" s="2"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D134" s="2"/>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D135" s="2"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D137" s="2"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C138" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D138" s="2"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C139" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D139" s="2"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C140" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D140" s="2"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C141" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D141" s="2"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D142" s="2"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C143" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D143" s="2"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D144" s="2"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D145" s="2"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C148" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D148" s="2"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C149" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D149" s="2"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D150" s="2"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C151" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D151" s="2"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C152" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D152" s="2"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C153" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D153" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D153" s="2"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D155" s="2"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C156" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D157" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D157" s="2"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C158" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D158" s="2"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C159" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D159" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D159" s="2"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C160" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D160" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D160" s="2"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D161" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D161" s="2"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C162" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D162" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D162" s="2"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D163" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D163" s="2"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C164" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D164" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D164" s="2"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D165" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D165" s="2"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C166" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D166" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D167" s="2"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D168" s="2"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C169" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D169" s="2"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D170" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D170" s="2"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C171" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D172" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D172" s="2"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D173" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C174" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D174" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D174" s="2"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D175" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D175" s="2"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C176" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D176" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D176" s="2"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C177" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C177" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D177" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D177" s="2"/>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C178" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D178" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D178" s="2"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="D179" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D179" s="2"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D180" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D180" s="2"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="D181" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D181" s="2"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D182" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D182" s="2"/>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C183" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D183" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D183" s="2"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C184" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D184" s="2"/>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="D185" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D185" s="2"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C186" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C186" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D186" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D186" s="2"/>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C187" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C187" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D187" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D187" s="2"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C188" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C188" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="D188" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D188" s="2"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C189" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D189" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C190" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="D190" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C191" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D191" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C192" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D192" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D192" s="2"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C193" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D193" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D193" s="2"/>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C194" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C194" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D194" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D194" s="2"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C195" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D195" s="2"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D196" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D196" s="2"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C197" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C197" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D197" s="2"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C198" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D198" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C199" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D199" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D199" s="2"/>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C200" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D200" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C201" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D201" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C202" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D202" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D202" s="2"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C203" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D203" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D203" s="2"/>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C204" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D204" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D204" s="2"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C205" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D205" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D205" s="2"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D206" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D206" s="2"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C207" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D207" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D207" s="2"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C208" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D208" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D208" s="2"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C209" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D209" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D209" s="2"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C210" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="D210" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D210" s="2"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C211" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D211" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C212" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D212" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D212" s="2"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C213" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D213" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="D214" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D214" s="2"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C215" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="D215" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D215" s="2"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C216" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D216" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D216" s="2"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C217" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D217" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D217" s="2"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D218" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D218" s="2"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="D219" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D219" s="2"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C220" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D220" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D220" s="2"/>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="D221" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D221" s="2"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C222" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="D222" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D222" s="2"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C223" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D223" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D223" s="2"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C224" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D224" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D224" s="2"/>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C225" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="D225" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D225" s="2"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C226" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D226" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D226" s="2"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C227" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C227" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="D227" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D227" s="2"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C228" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D228" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D228" s="2"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="D229" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D229" s="2"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C230" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="D230" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D230" s="2"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C231" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="D231" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D231" s="2"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C232" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D232" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D232" s="2"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C233" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C233" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="D233" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D233" s="2"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C234" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="D234" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D234" s="2"/>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D235" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D235" s="2"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="D236" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D236" s="2"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="D237" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D237" s="2"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C238" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C238" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="D238" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D238" s="2"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C239" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D239" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D239" s="2"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D240" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D240" s="2"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C241" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="D241" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D241" s="2"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C242" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C242" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="D242" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D242" s="2"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C243" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D243" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D243" s="2"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C244" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D244" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D244" s="2"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C245" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="D245" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D245" s="2"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C246" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C246" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D246" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D246" s="2"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C247" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D247" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D247" s="2"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="D248" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C249" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="D249" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D249" s="2"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C250" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C250" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D250" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D250" s="2"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C251" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C251" s="3" t="s">
+      <c r="D251" s="2"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="D251" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D252" s="2"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="0" t="s">
+        <v>502</v>
+      </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="0" t="s">
+        <v>503</v>
+      </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="0" t="s">
+        <v>504</v>
+      </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="0" t="s">
+        <v>505</v>
+      </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="0" t="s">
+        <v>506</v>
+      </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="0" t="s">
+        <v>507</v>
+      </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="0" t="s">
+        <v>508</v>
+      </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="0" t="s">
+        <v>509</v>
+      </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="0" t="s">
+        <v>510</v>
+      </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="0" t="s">
+        <v>511</v>
+      </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="0" t="s">
+        <v>512</v>
+      </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="0" t="s">
+        <v>513</v>
+      </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="0" t="s">
+        <v>515</v>
+      </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="0" t="s">
+        <v>516</v>
+      </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="0" t="s">
+        <v>517</v>
+      </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="0" t="s">
+        <v>518</v>
+      </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="0" t="s">
+        <v>519</v>
+      </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="0" t="s">
+        <v>521</v>
+      </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="0" t="s">
+        <v>523</v>
+      </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="0" t="s">
+        <v>524</v>
+      </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="0" t="s">
+        <v>525</v>
+      </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="0" t="s">
+        <v>526</v>
+      </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="0" t="s">
+        <v>527</v>
+      </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="0" t="s">
+        <v>528</v>
+      </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="0" t="s">
+        <v>529</v>
+      </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="0" t="s">
+        <v>530</v>
+      </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="0" t="s">
+        <v>531</v>
+      </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="0" t="s">
+        <v>532</v>
+      </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="0" t="s">
+        <v>533</v>
+      </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="0" t="s">
+        <v>534</v>
+      </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="0" t="s">
+        <v>535</v>
+      </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="0" t="s">
+        <v>536</v>
+      </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="0" t="s">
+        <v>537</v>
+      </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="0" t="s">
+        <v>538</v>
+      </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="0" t="s">
+        <v>539</v>
+      </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="0" t="s">
+        <v>540</v>
+      </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="0" t="s">
+        <v>541</v>
+      </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="0" t="s">
+        <v>542</v>
+      </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="0" t="s">
+        <v>543</v>
+      </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="0" t="s">
+        <v>544</v>
+      </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="0" t="s">
+        <v>545</v>
+      </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="0" t="s">
+        <v>546</v>
+      </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="0" t="s">
+        <v>547</v>
+      </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="0" t="s">
+        <v>548</v>
+      </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="0" t="s">
+        <v>549</v>
+      </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="0" t="s">
+        <v>550</v>
+      </c>
       <c r="D301" s="2"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="0" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="0" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="0" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="0" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="0" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="0" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="0" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="0" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="0" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="0" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="0" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="0" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="0" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="0" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="0" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="0" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="0" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="0" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="0" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="0" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="0" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="0" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="0" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="0" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="0" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="0" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="0" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="0" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="0" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="0" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="0" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="0" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="0" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="0" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="0" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="0" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="0" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="0" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="0" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="0" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="0" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="0" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="0" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="0" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="0" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="0" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="0" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="0" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="0" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="0" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="0" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="0" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="0" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="0" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="0" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="0" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="0" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="0" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="0" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="0" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="0" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="0" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="0" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="0" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="0" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="0" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="0" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="0" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="0" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="0" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="0" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="0" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="0" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="0" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="0" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="0" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="0" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="0" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="0" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="0" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="0" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="0" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="0" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="0" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="0" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="0" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="0" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="0" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="0" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="0" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="0" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="0" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="0" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="0" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="0" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="2" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="0" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="0" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="0" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="0" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="0" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="0" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="0" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="0" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="0" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="2" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="0" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="0" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="0" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="0" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="0" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="0" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="0" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="0" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="0" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="0" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="0" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="2" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="0" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="0" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="0" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="0" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="0" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="0" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="0" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="0" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="0" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="0" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="0" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="0" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="0" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="0" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="0" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A438" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="0" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A439" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="0" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A440" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="0" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A441" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="0" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="0" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A443" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="0" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A444" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="0" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A445" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="0" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A446" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="0" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A447" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="0" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A448" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="0" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A449" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="0" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A450" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="0" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A451" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="0" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A452" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" s="0" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A453" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="0" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A454" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="0" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A455" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="0" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A456" s="2" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="0" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A457" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="0" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A458" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="0" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A459" s="2" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="0" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="0" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" s="0" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" s="0" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" s="0" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A464" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" s="0" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A465" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="0" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="0" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="2" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="0" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A469" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="0" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="0" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="0" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="0" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="0" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="0" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="0" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="0" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A477" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="0" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A478" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="0" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="2" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="0" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="0" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="0" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="0" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A483" s="2" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="0" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A484" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="0" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A485" s="2" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="0" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A486" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="0" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="0" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="0" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="0" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="0" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A491" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="0" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="0" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A493" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="0" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A494" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="0" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A495" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="0" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A496" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="0" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A497" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="0" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A498" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="0" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="0" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="0" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="0" t="s">
+        <v>750</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>